--- a/Noticias_Calcario_20260719.xlsx
+++ b/Noticias_Calcario_20260719.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D508"/>
+  <dimension ref="A1:D507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,44 +441,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Galeria de Facade System - LINEA Dietfurt Limestone - 8 - ArchDaily</t>
+          <t>Proteína ajusta defesa vegetal à oferta de enxofre - Revista Cultivar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18/07/2026 21:52</t>
+          <t>19/07/2026 09:40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQV0JMRWxtTFRtQUxyejdKTmZzUjAteGkyQzl2MDBiQkRKdUxkMUlwN3R2OWFfUkhidnczdEJKZkdGTmMwSEhqVjcwZ1lmWWZVU0JOR0tMcGFoSUZ1Y3VsR3JrZFloLXJ3Uk9IYXJRRlRsNHMtNkNFMElDb1dlM19TQXdrYkF6TURlOXptQzFVS2c3WDZIRGxJeUVHSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOVGlUQzZ6UDhYaDg3ZUNHTEwwbDBZcTlnVUVGUTFkalFpLUpQSVRnSTZCOVFYcGlub0FBSWNSTGE2WEFfS0ZpdFNnZGZyU3hick90QmF2WmpIUWNYVVNqajhBVUZSREF3UVJtMzJKT25sVTZkVU1UQzhZR0VENFdMRTVfRU10dTNOSllMdHlraGllX056?oc=5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Terra - 1 - ArchDaily</t>
+          <t>Galeria de Facade System - LINEA Dietfurt Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>18/07/2026 20:16</t>
+          <t>18/07/2026 21:52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOa2Y4R1VBS3NJRDhtM2RhOUFBNE5EN2Y2bjBsOVJwSFZweE8wSExrYnZVUGtnRkU3czZ2WWppeGtob0M0SldGSXBXdlVYeVZWck9sWU80TmxLQkNEVWZfVjhuQWRvUkV4ZlAzUlN1S1hZbll4dEJUSDJoS2hNQzd2Y0h3WXgtMlF2RjRuS2dBdFBmZjAxazV5eFhZNU5wLUJRY3piTG5jZnEwS3BZZExtMDJ5WEFkUjNidjRnU2p5WHRCdllTVS1mRUU3MDN3MldyeTB2OVd6N1NoeXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQV0JMRWxtTFRtQUxyejdKTmZzUjAteGkyQzl2MDBiQkRKdUxkMUlwN3R2OWFfUkhidnczdEJKZkdGTmMwSEhqVjcwZ1lmWWZVU0JOR0tMcGFoSUZ1Y3VsR3JrZFloLXJ3Uk9IYXJRRlRsNHMtNkNFMElDb1dlM19TQXdrYkF6TURlOXptQzFVS2c3WDZIRGxJeUVHSQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 3 - ArchDaily</t>
+          <t>Galeria de Mosaic Tiles - Terra - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18/07/2026 19:08</t>
+          <t>18/07/2026 20:16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNcVZaa1o2bzBOYmxiQkdxLTk4QmxmV2RxMHNBX1pQd2Y0SkJ3ekhOMk91Y29KRl9zeFZpcFJ0SnJkWlFNWnA5S0dNejZUX3MweERUQVFUOHVxRlhnamlrUEsweE4yYmw3b3F3Wl9HMmhqTFowMGJreHlIemtqcXZHbzlFZmQ4R2I3OVhkb2RTOWx4X28zbHdHMWtlZUtwZVNoVjlSMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOa2Y4R1VBS3NJRDhtM2RhOUFBNE5EN2Y2bjBsOVJwSFZweE8wSExrYnZVUGtnRkU3czZ2WWppeGtob0M0SldGSXBXdlVYeVZWck9sWU80TmxLQkNEVWZfVjhuQWRvUkV4ZlAzUlN1S1hZbll4dEJUSDJoS2hNQzd2Y0h3WXgtMlF2RjRuS2dBdFBmZjAxazV5eFhZNU5wLUJRY3piTG5jZnEwS3BZZExtMDJ5WEFkUjNidjRnU2p5WHRCdllTVS1mRUU3MDN3MldyeTB2OVd6N1NoeXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -512,105 +512,105 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Aqualuxe - 4 - ArchDaily</t>
+          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>18/07/2026 13:49</t>
+          <t>18/07/2026 19:08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnBnX1FxQ2lyT3U3bGFrTzBXMTZJNlV4MjhYT2tFUlpkYm5za1NlQTNKZXd4R21RUi11My1xVzNrRzZ5RzNEcDUxV0wwMnRxcFBha0ZZOTFzMnpwZ2kwNTRTbGttTGc3bUMwSkQxYTZMN2l5SmdYTG9DRUp3QU1VRVc2SURDY3BSUkNkWVJjSUY4ZjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNcVZaa1o2bzBOYmxiQkdxLTk4QmxmV2RxMHNBX1pQd2Y0SkJ3ekhOMk91Y29KRl9zeFZpcFJ0SnJkWlFNWnA5S0dNejZUX3MweERUQVFUOHVxRlhnamlrUEsweE4yYmw3b3F3Wl9HMmhqTFowMGJreHlIemtqcXZHbzlFZmQ4R2I3OVhkb2RTOWx4X28zbHdHMWtlZUtwZVNoVjlSMw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
+          <t>Galeria de Mosaic Tiles - Aqualuxe - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18/07/2026 12:05</t>
+          <t>18/07/2026 13:49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPRnBnX1FxQ2lyT3U3bGFrTzBXMTZJNlV4MjhYT2tFUlpkYm5za1NlQTNKZXd4R21RUi11My1xVzNrRzZ5RzNEcDUxV0wwMnRxcFBha0ZZOTFzMnpwZ2kwNTRTbGttTGc3bUMwSkQxYTZMN2l5SmdYTG9DRUp3QU1VRVc2SURDY3BSUkNkWVJjSUY4ZjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
+          <t>Na China, um sumidouro de 192 metros esconde árvores de 40 metros e três cavernas sob uma paisagem de calcário - Revista Oeste</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18/07/2026 03:44</t>
+          <t>18/07/2026 12:05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQQ203UGF1QlY0cDdHcXY1bFpSazZmZG1VbXR1ZkRHcTFqX0UtYUdLLTRDR2Q3anBfYlpBZ1lBUnhjM2x0TFkzWTdnRm5QZDQtbzlRcHRpR0d6TWliQ1dTSkZBSUxYMmhoZldSZ2RZZDZLWUZ4NmxLUlRITlNObUxOLTc2UzdqTVRTdE1DSVY0d0xxeHlVSEdFbXNiNnBQcmhSYTVmbkFBc19FMzBJQ2g0SXY5VDBDclBxYVZFZUxtanlHaGtGS2FJVG9wUTdBTVduVUJqSzd4ZHNHcUcyVUJHaUx6bzc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOaXc5OTRzUXRXT1o0cFpOZE9jbnoyVUpVTzZ6QzBaaFZVNVZfbDJ0YnA5RHNTdmFrMmlTUWNGbHNqQ1ZoY0hpZE53U3EyVEJQU2RDMUtzYUs0c0Q3aG9FTl9RaWlFVUY0cjA5RlFPZGM4anVmeDRYdlhQQ05WRnZNNXFsQ2x1eGxfcU1sS0F6X0RCRjVHOWhwYWZQdUdGN2tQQWF0QU9xZnAxM3JqQjFYUUtILVRaSW8yQlMwQVBRa3VCWWFBdWVrc0dURTY0OUhydGt2WUs5Y3NkRjhjUWVidzVKVGVsaTRlY0VyVS1R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
+          <t>Coco ralado com excesso de enxofre: quais os riscos? Em quais sintomas prestar atenção? - Estadão</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18/07/2026 01:44</t>
+          <t>18/07/2026 03:44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQQ203UGF1QlY0cDdHcXY1bFpSazZmZG1VbXR1ZkRHcTFqX0UtYUdLLTRDR2Q3anBfYlpBZ1lBUnhjM2x0TFkzWTdnRm5QZDQtbzlRcHRpR0d6TWliQ1dTSkZBSUxYMmhoZldSZ2RZZDZLWUZ4NmxLUlRITlNObUxOLTc2UzdqTVRTdE1DSVY0d0xxeHlVSEdFbXNiNnBQcmhSYTVmbkFBc19FMzBJQ2g0SXY5VDBDclBxYVZFZUxtanlHaGtGS2FJVG9wUTdBTVduVUJqSzd4ZHNHcUcyVUJHaUx6bzc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Tiles - Through the Seven Seas - 4 - ArchDaily</t>
+          <t>Galeria de Flooring and Wall Tiles - Dietfurt Limestone - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18/07/2026 00:46</t>
+          <t>18/07/2026 01:44</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOWXJZMk5remlBSFU4WEY0TEtEcDhQNXVvRm9KemsyakoxYWpOU2pHdFdCUzg2SXdMc09MVkRVdlZ0VTV4TGY0anlPUG9KZmpla28wRlJDY3RqbVNvMEhQY0xyUG8zeWp2WjdZY19GNzFOV19MQjA5WUwxb1ZEbkhVQVc5LXEtQ0lNSk91N1hpczhVTDNBRDlPT25PczQwTTlvMzhfYWhwZVRxUWJEdWJNM0ctSGxaU2xSdHE3STdkdDZTcUk2dWJFdlJRMmFDUU5TbXZ5WDNLOEhqVzdEODhkX0hfYnpUQXlfUncwUllFbjlxUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxPZVRlQ1V1aUlpcmFSQ0ZIOWU3S1JSM2xNWDhwazQ3cmx1MHQ4aWt2dFc4a1pNbmNDNWJCUkR4RXZ1T1NEYkRpVVpkN3pyRnVXdmNZejhyRmtJcTFROTYtQjRqYnBkSkZ3ODBFSlNFVngtOXNqTDJBYmt5Si10YmVUT01pdWtNSFkwR3RYZVJ1TTk0X2ljeXRMRW1nVGgwTjNNYUUzeFdXR3p5NEc3Sk9pbHBMREl3eV8yZVlDc0dIdXBRVjRTQUtyZ2tsa3FXZDdsZW45NDFOOVBMOXdkakFKYklRdDlUWmtRUTNVMnY3R3NQNTZkRFE1N1VDRWRrRWNoQ1Q2T2ln?oc=5</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Galeria de Wall and Floor Tiles - Les Classiques Collection - 18 - ArchDaily</t>
+          <t>Galeria de Mosaic Tiles - Through the Seven Seas - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17/07/2026 22:52</t>
+          <t>18/07/2026 00:46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQQWNuMXVfUks2YlRWS0N5dzg4MUJjaklFUjN4WE1kZEtkcDNaeDE4Tm5saVYxbW5xbnlkeVpET0l1XzFacHdXZWliQmhUOFd1UlpOUDlOdDcxOXRFaV9Qd3BtdW5EUEZZUXZKTmttOFFOaTBQUWM3dFBxd19PYkNzTGEzOTh0aDVPalJ5V3NNSjVzNFhqQmxiN3B2SXl5ZkJibm1WNW9kcHVZZENDSlRub3Z6SjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOWXJZMk5remlBSFU4WEY0TEtEcDhQNXVvRm9KemsyakoxYWpOU2pHdFdCUzg2SXdMc09MVkRVdlZ0VTV4TGY0anlPUG9KZmpla28wRlJDY3RqbVNvMEhQY0xyUG8zeWp2WjdZY19GNzFOV19MQjA5WUwxb1ZEbkhVQVc5LXEtQ0lNSk91N1hpczhVTDNBRDlPT25PczQwTTlvMzhfYWhwZVRxUWJEdWJNM0ctSGxaU2xSdHE3STdkdDZTcUk2dWJFdlJRMmFDUU5TbXZ5WDNLOEhqVzdEODhkX0hfYnpUQXlfUncwUllFbjlxUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
+          <t>Galeria de Wall and Floor Tiles - Les Classiques Collection - 18 - ArchDaily</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17/07/2026 20:47</t>
+          <t>17/07/2026 22:52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQQWNuMXVfUks2YlRWS0N5dzg4MUJjaklFUjN4WE1kZEtkcDNaeDE4Tm5saVYxbW5xbnlkeVpET0l1XzFacHdXZWliQmhUOFd1UlpOUDlOdDcxOXRFaV9Qd3BtdW5EUEZZUXZKTmttOFFOaTBQUWM3dFBxd19PYkNzTGEzOTh0aDVPalJ5V3NNSjVzNFhqQmxiN3B2SXl5ZkJibm1WNW9kcHVZZENDSlRub3Z6SjA?oc=5</t>
         </is>
       </c>
     </row>
@@ -666,171 +666,171 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
+          <t>Melhora no poder de compra de fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17/07/2026 20:33</t>
+          <t>17/07/2026 20:47</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNY0VhZGVublZBbnlpeHVObmRmeXV0dzlUT0FwXzZBSzNqUWh5U3FqMThXOXY0UW81X09wanNPWk9FVk4tU2lhcmFwQWdtR1FYTjk4eG1SdE9XM3NFWkxTRGRjcGJ2RVdpcm9NMTRXTUlGazdWbkJydWVsUXgwWTZOcGNFQUhBQ0haTzRFOEJTSml2U1U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hoje (17) é o único dia para usar este emoji; saiba por que - Rádio Itatiaia</t>
+          <t>Bolsa de qualificação pode evitar demissões na Mosaic - JM Online</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17/07/2026 16:38</t>
+          <t>17/07/2026 20:33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVzdHejhmUG55VFgxVUZObFNYZ0psSU5Zb2Znc1FIcTRET19tem50R2N1SlpwbG1IWm5QU2gwLXJLdGdGSE1BZVV3dVV2Zm4wc2c1UUs4ZnRLREtTRmM0VFNZSGtLMTBnSEtSQVVIRGkzSW5ySG91TloxU282RWlHZ3N2azVQWTh6UEtCenBBTTZmWXZseGZ3eVN2bjk0bFBZU0tUd21neWtlUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdDRaT2xrcWlGbVdCNTZYcVNOVEt0Sm9vSHNGOVdReWFsOUhrV0pYdjZ4MkRFSWQ3LUFkVmUxelQ1eTA1Z3Rqel9SLUxRYkQ5dng1V2pxSEhsbTJwWE9aMnI4dC1ueE8yWlZRbVVJRUluY21wQlk2azN6bUU3eEpTeFUwNXhZMTkzOHk3aGJjQkxsbkdGaFJZNUl2QdIBowFBVV95cUxNQkhuT3ZUMy1Qemh6NVRtazBZUmJ4SXg4WDZiaFhXMFY5WkJkc1ZiVUlLUWpteGdpVDc5YjhjdW1RejlyVUlrX0JacGFtLTctSWc2M09ta21ISlJTeVl2WGh5bFUtTTlfM004LTNwZ0M5UV9SRXBmb1NXVExmc3ZsYmJoclN5SzFMUEpfcGhaLXRJbGllQkZrdXcxSjVfVTNoRVdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Galeria de Mosaic Walkway in Punta de Mita Hotel - 2 - ArchDaily</t>
+          <t>Hoje (17) é o único dia para usar este emoji; saiba por que - Rádio Itatiaia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17/07/2026 12:08</t>
+          <t>17/07/2026 16:38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPMmxUNlo2MFE2Rkxhdkh6U19sZjdFWV9DSGl5SThBYVRFWjdNY2RUS2RMVVFpbXJNaWU3SE9mT0VuRTJITl91Z2R0eF9KeVVRektwd2lBa1BUclEzaWtPbXkxVFZFLWg2MVJ4UUdoakZ3ampmc25aRkJqa2d4SjdYR1RPaTQ1LW5Cc012R1lKTm1aQ25Db3IxaEpjaWJWRm5lRjFvdHpUOXFhYS1oVlVnbzBCaHVXNzlSZ1FBNjJfQnp4SFVweHpJdWpqd2xZc0gwTTFrZHZDX05oRU5zWkhFME5XZEhSRU1PY3pqWDk1QkhuakhG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPVzdHejhmUG55VFgxVUZObFNYZ0psSU5Zb2Znc1FIcTRET19tem50R2N1SlpwbG1IWm5QU2gwLXJLdGdGSE1BZVV3dVV2Zm4wc2c1UUs4ZnRLREtTRmM0VFNZSGtLMTBnSEtSQVVIRGkzSW5ySG91TloxU282RWlHZ3N2azVQWTh6UEtCenBBTTZmWXZseGZ3eVN2bjk0bFBZU0tUd21neWtlUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
+          <t>Galeria de Mosaic Walkway in Punta de Mita Hotel - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17/07/2026 10:55</t>
+          <t>17/07/2026 12:08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPMmxUNlo2MFE2Rkxhdkh6U19sZjdFWV9DSGl5SThBYVRFWjdNY2RUS2RMVVFpbXJNaWU3SE9mT0VuRTJITl91Z2R0eF9KeVVRektwd2lBa1BUclEzaWtPbXkxVFZFLWg2MVJ4UUdoakZ3ampmc25aRkJqa2d4SjdYR1RPaTQ1LW5Cc012R1lKTm1aQ25Db3IxaEpjaWJWRm5lRjFvdHpUOXFhYS1oVlVnbzBCaHVXNzlSZ1FBNjJfQnp4SFVweHpJdWpqd2xZc0gwTTFrZHZDX05oRU5zWkhFME5XZEhSRU1PY3pqWDk1QkhuakhG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 12 - ArchDaily</t>
+          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17/07/2026 10:47</t>
+          <t>17/07/2026 10:55</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOVG5QeHc1MVllRXpLZGR1REtSVWZxMi12LUdudEh5My1CN3lKc1dCd0U4SFdjWTE1RWF1cUJYbk5ZTEppUkkycm45U3VSRldONnFLV3RONGFTZG5XS2ZWdkIwNjJVeEFLRGdleGU5ZWFoeWpyTzNZN0tCQ2NCM3BJWl9laF9kVG5BcmVVVWp1RnFjOEhXYTNqSFJCN0NJMkxSa09lZldnUHhma052SDAzNlJLSFQ0bkUyUWJGYU1kZHhyemJpd2N4ZlZwcDE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cenário de fertilizantes muda ritmo de compras para a safrinha - Notícias Agrícolas</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 12 - ArchDaily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17/07/2026 10:27</t>
+          <t>17/07/2026 10:47</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxON0dJME8xS25sbnpoR1FvRkhycURDMlJ0Yk8tdHpTTHUyOEVnbkEwRWpuaklvanZmUmdpTGdHZkNxM3JETVp0bVlMbjRvdXBpd3Rmdjl4SlRsakEyVi1yQm5xR1pPTWFfMnBKUEpwUC1wWjdYRHhtTWV1OUU4U2QzX1o4WWFBQUhSYVZxTHMzQ1ZuLUpXcklfSUlHU21yQ0NxUDdkdVF6R0poVk54NmVpTHowbkRvNW9PQlFnWEREVEp6Y2plSW1kNG5tLXQ5Z2hZZUHSAdIBQVVfeXFMTjdHSTBPMUtubG56aEdRb0ZIcnFEQzJSdGJPLXR6U0x1MjhFZ25BMEVqbmpJb2p2ZlJnaUxnR2ZDcTNyRE1adG1ZTG40b3VwaXd0ZnY5eEpUbGpBMlYtckJucUdaT01hXzJwSlBKcFAtcFo3WER4bU1ldTlFOFNkM19aOFlhQUFIUmFWcUxzM0NWbi1KV3JJX0lJR1NtckNDcVA3ZHVRekdKaFZOeDZlaUx6MG5EbzVvT0JRZ1hERFRKemNqZUltZDRubS10OWdoWWVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOVG5QeHc1MVllRXpLZGR1REtSVWZxMi12LUdudEh5My1CN3lKc1dCd0U4SFdjWTE1RWF1cUJYbk5ZTEppUkkycm45U3VSRldONnFLV3RONGFTZG5XS2ZWdkIwNjJVeEFLRGdleGU5ZWFoeWpyTzNZN0tCQ2NCM3BJWl9laF9kVG5BcmVVVWp1RnFjOEhXYTNqSFJCN0NJMkxSa09lZldnUHhma052SDAzNlJLSFQ0bkUyUWJGYU1kZHhyemJpd2N4ZlZwcDE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Após polêmica da maconha, Piovani detona Virginia e chama de "loira de laboratório": "Cheiro de enxofre" - Folha Vitória</t>
+          <t>Cenário de fertilizantes muda ritmo de compras para a safrinha - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17/07/2026 07:47</t>
+          <t>17/07/2026 10:27</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTmh6UXNDdlRkVklBdWpzaWVtc1ZGZk5aVzNTMGRGeXN0MFlrMWktN2Jnd3hEdFJYMnJuV2VvQ3ViWG9YNVYwNzh2TWZwT2pFcDZpVHBFcHpvaHMyN2o0X2t2bzF0b1VNN3pmdlNENjAwNmd0enk4bjNqSHNVSFMwMFdnYTNDREMyZzdfRUQ2WFAyNGNiVURxaExPQU01enlFbU1XTHNyVnFWdUtiSlhLLUczYWNiUExDZWNOS1kwRTdfcmtjZ0RCQlEzbnVXYlNSSk5CdjhGakFfZ001SGIzbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxON0dJME8xS25sbnpoR1FvRkhycURDMlJ0Yk8tdHpTTHUyOEVnbkEwRWpuaklvanZmUmdpTGdHZkNxM3JETVp0bVlMbjRvdXBpd3Rmdjl4SlRsakEyVi1yQm5xR1pPTWFfMnBKUEpwUC1wWjdYRHhtTWV1OUU4U2QzX1o4WWFBQUhSYVZxTHMzQ1ZuLUpXcklfSUlHU21yQ0NxUDdkdVF6R0poVk54NmVpTHowbkRvNW9PQlFnWEREVEp6Y2plSW1kNG5tLXQ5Z2hZZUHSAdIBQVVfeXFMTjdHSTBPMUtubG56aEdRb0ZIcnFEQzJSdGJPLXR6U0x1MjhFZ25BMEVqbmpJb2p2ZlJnaUxnR2ZDcTNyRE1adG1ZTG40b3VwaXd0ZnY5eEpUbGpBMlYtckJucUdaT01hXzJwSlBKcFAtcFo3WER4bU1ldTlFOFNkM19aOFlhQUFIUmFWcUxzM0NWbi1KV3JJX0lJR1NtckNDcVA3ZHVRekdKaFZOeDZlaUx6MG5EbzVvT0JRZ1hERFRKemNqZUltZDRubS10OWdoWWVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
+          <t>Após polêmica da maconha, Piovani detona Virginia e chama de "loira de laboratório": "Cheiro de enxofre" - Folha Vitória</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17/07/2026 05:20</t>
+          <t>17/07/2026 07:47</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTmh6UXNDdlRkVklBdWpzaWVtc1ZGZk5aVzNTMGRGeXN0MFlrMWktN2Jnd3hEdFJYMnJuV2VvQ3ViWG9YNVYwNzh2TWZwT2pFcDZpVHBFcHpvaHMyN2o0X2t2bzF0b1VNN3pmdlNENjAwNmd0enk4bjNqSHNVSFMwMFdnYTNDREMyZzdfRUQ2WFAyNGNiVURxaExPQU01enlFbU1XTHNyVnFWdUtiSlhLLUczYWNiUExDZWNOS1kwRTdfcmtjZ0RCQlEzbnVXYlNSSk5CdjhGakFfZ001SGIzbg?oc=5</t>
         </is>
       </c>
     </row>
@@ -842,161 +842,161 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
+          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17/07/2026 03:58</t>
+          <t>17/07/2026 05:20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 31 - ArchDaily</t>
+          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17/07/2026 01:57</t>
+          <t>17/07/2026 03:58</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQT2NkakNmbkgzalhHVXJQbk1jUFhaYldjUDY5bzd5dk5rUGpNZDVwcUs4UGZnb2dSSmx1OHowbUppbmhEWjZkSnBmTnJFQlFEWjhKSVdFS0JuSVRSdkJWOHVnUzRFS2NXRER2eEpIUllodnRJZ2Z3d19CZ0k4TmNJV3lmd3pzaG1na1BXeDE2TWMtUEVrYWNNOUNYSmYwYnRvLU45UUxTQ0tKa1F5VFY5cDBxVWtlbnlFeWhHWVVYSEdUQTd5R0Zld0J0NndycjU5aXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Galeria de Porcelain Mosaics – Olympic Series - 3 - ArchDaily</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 31 - ArchDaily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16/07/2026 22:13</t>
+          <t>17/07/2026 01:57</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQY1RfYzB5QWNIUm02bHM2NndzWnM3TnF3TjI2Y2ZabkFnYVpBeS1YUUpYNnNHZm52Q3BUNjlNaGp4eXZxbEloT2RVTDF4TUtnQ1NpRDBtUWQ5MmNrTkxQQ0FENlhFYks3d2otT1dwcnVMakhtSm5OUV9VY0ZwaVhoTGFLLVBZVzNiUmhSR3RhdTYzQWl4clJhYXJqQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQT2NkakNmbkgzalhHVXJQbk1jUFhaYldjUDY5bzd5dk5rUGpNZDVwcUs4UGZnb2dSSmx1OHowbUppbmhEWjZkSnBmTnJFQlFEWjhKSVdFS0JuSVRSdkJWOHVnUzRFS2NXRER2eEpIUllodnRJZ2Z3d19CZ0k4TmNJV3lmd3pzaG1na1BXeDE2TWMtUEVrYWNNOUNYSmYwYnRvLU45UUxTQ0tKa1F5VFY5cDBxVWtlbnlFeWhHWVVYSEdUQTd5R0Zld0J0NndycjU5aXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
+          <t>Galeria de Porcelain Mosaics – Olympic Series - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16/07/2026 20:53</t>
+          <t>16/07/2026 22:13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQY1RfYzB5QWNIUm02bHM2NndzWnM3TnF3TjI2Y2ZabkFnYVpBeS1YUUpYNnNHZm52Q3BUNjlNaGp4eXZxbEloT2RVTDF4TUtnQ1NpRDBtUWQ5MmNrTkxQQ0FENlhFYks3d2otT1dwcnVMakhtSm5OUV9VY0ZwaVhoTGFLLVBZVzNiUmhSR3RhdTYzQWl4clJhYXJqQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Galeria de Porcelain Mosaics – Olympic Series - 4 - ArchDaily</t>
+          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16/07/2026 18:02</t>
+          <t>16/07/2026 20:53</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNaUw5R1NLTUlpMWxBYmhvVWN5V1hUaVJjTVJXTHJwajg4UTN6bThCSXMybkhVTjZ5WGw0T2N1SUNpOUFybnFJaEN6Q1NKOF95R2JSNjdCTU1oVmlLOU96cjNFdGJfWEpBY0dJSXVPY1ZOSlZDLVo5c3U0SGdCYTExdlpmY0dOY3E4YmxHSDlLUVpsanJSY0FMN3JSaHFZclBmeTkxWlJFRHR5TExpU3R4d0dhcW1fcm9VV0FnSGFFYjRONkNfSkVOTll1VXBLa3VfcnRoMlRYR2pkOFFUTFljZFd0UEhGN2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
+          <t>Galeria de Porcelain Mosaics – Olympic Series - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16/07/2026 17:18</t>
+          <t>16/07/2026 18:02</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNaUw5R1NLTUlpMWxBYmhvVWN5V1hUaVJjTVJXTHJwajg4UTN6bThCSXMybkhVTjZ5WGw0T2N1SUNpOUFybnFJaEN6Q1NKOF95R2JSNjdCTU1oVmlLOU96cjNFdGJfWEpBY0dJSXVPY1ZOSlZDLVo5c3U0SGdCYTExdlpmY0dOY3E4YmxHSDlLUVpsanJSY0FMN3JSaHFZclBmeTkxWlJFRHR5TExpU3R4d0dhcW1fcm9VV0FnSGFFYjRONkNfSkVOTll1VXBLa3VfcnRoMlRYR2pkOFFUTFljZFd0UEhGN2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
+          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16/07/2026 15:34</t>
+          <t>16/07/2026 17:18</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
+          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1006,29 +1006,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Queda da ureia melhora poder de compra, mas fosfatados ainda preocupam - boca.com.br</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>16/07/2026 15:22</t>
+          <t>16/07/2026 15:34</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQVkdGck5rMVc3aHBKRkVTVDY1YjhUVWdfenJCV3dBVGdVTlhkZmlNcVhFdkVnUUkwQURQMklOTVpXeGJyaHFvRUxEZDg4RUlGV1hzUl9QWElBYWRRcllDc3hEb1pKZkcxa0UzZlNnUnZULTFsWjZrLW9HbzJEbDBwU21Kd2xLaDljRFR5ZGEtXzhBNHpGLTJuOTRLbXNRX3BDZ0Vv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
         </is>
       </c>
     </row>
@@ -1040,325 +1040,325 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
+          <t>Queda da ureia melhora poder de compra, mas fosfatados ainda preocupam - boca.com.br</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16/07/2026 15:09</t>
+          <t>16/07/2026 15:22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQVkdGck5rMVc3aHBKRkVTVDY1YjhUVWdfenJCV3dBVGdVTlhkZmlNcVhFdkVnUUkwQURQMklOTVpXeGJyaHFvRUxEZDg4RUlGV1hzUl9QWElBYWRRcllDc3hEb1pKZkcxa0UzZlNnUnZULTFsWjZrLW9HbzJEbDBwU21Kd2xLaDljRFR5ZGEtXzhBNHpGLTJuOTRLbXNRX3BDZ0Vv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
+          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16/07/2026 14:06</t>
+          <t>16/07/2026 15:09</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
+          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16/07/2026 14:01</t>
+          <t>16/07/2026 14:06</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec24ca04f81b8794fa763fc1a7d&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - Goiás 246</t>
+          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16/07/2026 13:33</t>
+          <t>16/07/2026 14:01</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPbnVDTmstaWFnRGV3S3R1MTM0QXdmUGpHanN1cE81NUdacmgwWFdhSlhnVHVGNnhFNUZWaEprTWh3MElybnVhajViRjY3bENySkUtMjlfLTJuN3VWTXcza2hpbGxtc1MyaXZ5clNVT1hGME9tOGVPWGp4QTlfV1hWQ1VTUERzWjBjLWwzLUpncnFsUkd1UVhCNUJBT2RxamhpYVpGbzBZd1dTLUtfdDVjNXJXNkZycnZiSXdsWjFpX3A0RVFZSV9HVE14T2FVbVRueHpMQzJsYmttOGowMkRROXVZdGFnV2VXamg2THVWenk?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbaf51c4b9abeeff07e3a4b2af8&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
+          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - Goiás 246</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16/07/2026 13:21</t>
+          <t>16/07/2026 13:33</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxPbnVDTmstaWFnRGV3S3R1MTM0QXdmUGpHanN1cE81NUdacmgwWFdhSlhnVHVGNnhFNUZWaEprTWh3MElybnVhajViRjY3bENySkUtMjlfLTJuN3VWTXcza2hpbGxtc1MyaXZ5clNVT1hGME9tOGVPWGp4QTlfV1hWQ1VTUERzWjBjLWwzLUpncnFsUkd1UVhCNUJBT2RxamhpYVpGbzBZd1dTLUtfdDVjNXJXNkZycnZiSXdsWjFpX3A0RVFZSV9HVE14T2FVbVRueHpMQzJsYmttOGowMkRROXVZdGFnV2VXamg2THVWenk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16/07/2026 11:16</t>
+          <t>16/07/2026 13:21</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quinta-feira 16 de Julho de 2026 - RRMAIS</t>
+          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>16/07/2026 10:25</t>
+          <t>16/07/2026 11:16</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNMTVOXzVPNXhnSmZNUnJHQXlabGw1RFVZYkxzLTNoSmxEWllHSzBPSG52bWg2UVdRRUp0eEk5ODdGbDJaX0psUzk4RHYzb1FRMkF2eEh6dTNsTXcxLWNILUdwOF9mQk82TV9zX0V5Tnpnam9jTzhfQWJJRi1jcUk0c0pxRG5icUtSdWRJMWxLNldLbmZsdWJZV3dBbzN1S3RTYkpIZEROZWJ0UmNM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>Cotações Agrícolas para esta Quinta-feira 16 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>16/07/2026 09:14</t>
+          <t>16/07/2026 10:25</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNMTVOXzVPNXhnSmZNUnJHQXlabGw1RFVZYkxzLTNoSmxEWllHSzBPSG52bWg2UVdRRUp0eEk5ODdGbDJaX0psUzk4RHYzb1FRMkF2eEh6dTNsTXcxLWNILUdwOF9mQk82TV9zX0V5Tnpnam9jTzhfQWJJRi1jcUk0c0pxRG5icUtSdWRJMWxLNldLbmZsdWJZV3dBbzN1S3RTYkpIZEROZWJ0UmNM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Galeria de Natural Stone - 2 - ArchDaily</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>16/07/2026 06:49</t>
+          <t>16/07/2026 09:14</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOWF1N2oyS0I0eEhqYWlycGUwT3NBakltcWhXTkUxb1RiSS1KaGVsa3VBcXB2eGRYXzhUTUVwX0RTbkhVRm95OE4wb3BrLXlhWVBScVVGXzhBQVg0ZHFnSnlpZ1BVbFZ6OWRpblBqY3FPLTlyeGJrLXczZ3gtTUJ5NFRDNDZsaXdfTnVvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Prevê-se que os preços globais da ureia permaneçam elevados, podendo duplicar os lucros da Ca Mau Fertilizer (DCM) este ano. - Vietnam.vn</t>
+          <t>Galeria de Natural Stone - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16/07/2026 04:00</t>
+          <t>16/07/2026 06:49</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMVhIc1NkVGp5Vi1SclM2Yldza3djbXF2UnJsU0NNXzdhVjIwUXFVUzA0S3ZrTmlzdnNhNUdrQmIwUmtaVUthcGI3ZGUwLUt6MEMtUTZNSmUwQndfQ2Q3ZnF0SjlvTVBLOFFOZldiSnFlQTBqVzl5bGt6ekVyaUJpcmc1ZGlWWUVNVk8td0VUTHpiX0FRRTdUOEdIRVYyRjNN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNOWF1N2oyS0I0eEhqYWlycGUwT3NBakltcWhXTkUxb1RiSS1KaGVsa3VBcXB2eGRYXzhUTUVwX0RTbkhVRm95OE4wb3BrLXlhWVBScVVGXzhBQVg0ZHFnSnlpZ1BVbFZ6OWRpblBqY3FPLTlyeGJrLXczZ3gtTUJ5NFRDNDZsaXdfTnVvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
+          <t>Prevê-se que os preços globais da ureia permaneçam elevados, podendo duplicar os lucros da Ca Mau Fertilizer (DCM) este ano. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>16/07/2026 02:55</t>
+          <t>16/07/2026 04:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQMVhIc1NkVGp5Vi1SclM2Yldza3djbXF2UnJsU0NNXzdhVjIwUXFVUzA0S3ZrTmlzdnNhNUdrQmIwUmtaVUthcGI3ZGUwLUt6MEMtUTZNSmUwQndfQ2Q3ZnF0SjlvTVBLOFFOZldiSnFlQTBqVzl5bGt6ekVyaUJpcmc1ZGlWWUVNVk8td0VUTHpiX0FRRTdUOEdIRVYyRjNN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Galeria de Natural Stone - 3 - ArchDaily</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15/07/2026 20:26</t>
+          <t>16/07/2026 02:55</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOM3BvdVRNTzcxbU56MnhqZ0RVNzhBTGZ1azBibUxGUmttR2NGQ05SdEhKSjBpYVk4Sk5PN3Q1b0FkYUdqYTl1SWpUM05tRXNZUm45aV9pQmROYWM5M1JXYVgzb3NsbVcwYjg3ZkVSMTEyYjVUY0tqdkF0M0xkNlB6X3g0QXNINHZBMGcwV0E0cWVUOGxkXzVuOERfVDdrdGg1SFZkZDFtTEl6bHJPYmRIZGI4cldFVVlCUHJVVHhBVWJTYndYMkgzRkdmVmcxMVJleUQ0OWoySDk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
+          <t>Galeria de Natural Stone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15/07/2026 20:03</t>
+          <t>15/07/2026 20:26</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOM3BvdVRNTzcxbU56MnhqZ0RVNzhBTGZ1azBibUxGUmttR2NGQ05SdEhKSjBpYVk4Sk5PN3Q1b0FkYUdqYTl1SWpUM05tRXNZUm45aV9pQmROYWM5M1JXYVgzb3NsbVcwYjg3ZkVSMTEyYjVUY0tqdkF0M0xkNlB6X3g0QXNINHZBMGcwV0E0cWVUOGxkXzVuOERfVDdrdGg1SFZkZDFtTEl6bHJPYmRIZGI4cldFVVlCUHJVVHhBVWJTYndYMkgzRkdmVmcxMVJleUQ0OWoySDk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 4 - ArchDaily</t>
+          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15/07/2026 19:35</t>
+          <t>15/07/2026 20:03</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNV3RZZUJQa0VwdjVXVU4zazZzRHN5WHE2YV9FN1IzcFFoS0U5VnIzOUQ1TkZlMmMydWFBbUwtWm9uY3NyREtEUlNnRFRKZGhpbW1QSGJRSzVjZmhfdTg3WmNWbjJHRWxqaGoyb1lXb0IwUFd2S2tvNnRiR3BLQW5BdERHR2tKQS00Rm4zMWtVZmJOaTR0S2pmNFFHbnJMc3VCdVpyaA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' do futuro dela - Notícias ao Minuto Brasil</t>
+          <t>Galeria de EchoPanel® Mosaic Acoustic Panel - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15/07/2026 18:11</t>
+          <t>15/07/2026 19:35</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNk9oVWZycVZaTy1oVlZoZl91VnE1U0tINURDVk1MeG0ydUNUMnY0dmJ2Tk1pc3h6ZTB6aGZ3UUpIRTF5dDQyenpMTzB3VDBfOUJJUVkzcWwzTFRBTUlSUEd5a2NsODZ0QUQ0VjZacC1BWnI3dVFNb3l0ejBVVk5HVGd2RjZEcng0LXlnT2pmcmExUVVlODFXUjB4akFKZnFBc19sRlpKcThZUmtpdTZCVS1EN3RzUW9rUDRyamZJWWh5QXlxRUR3dG5MTTNvWExVa1N6TnJSdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNV3RZZUJQa0VwdjVXVU4zazZzRHN5WHE2YV9FN1IzcFFoS0U5VnIzOUQ1TkZlMmMydWFBbUwtWm9uY3NyREtEUlNnRFRKZGhpbW1QSGJRSzVjZmhfdTg3WmNWbjJHRWxqaGoyb1lXb0IwUFd2S2tvNnRiR3BLQW5BdERHR2tKQS00Rm4zMWtVZmJOaTR0S2pmNFFHbnJMc3VCdVpyaA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1370,61 +1370,61 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>“Loira feita em laboratório”: Piovani detona Virginia de novo e fala em “cheiro de enxofre” - Jornal de Brasília</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e diz sentir 'cheiro de enxofre' do futuro dela - Notícias ao Minuto Brasil</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>15/07/2026 16:45</t>
+          <t>15/07/2026 18:11</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNT1kzRjVZWWdPSDgwOGhBYXMtYk9ob0lyNUV6SFdCa3FuVkFYdlhxT1hFREc1N3V2R0lTa01qSFpnVXJNTlY4eGNudVdDenZlelZPY2lHcGlkV3lOYVgwVVo2aVVlcWRxZ2ZLelg3dW5nWmVERG94SlFZNXREaGZWaTN4RmN4dnRsRWtaT1J6ZmlUU190b1hWNlUtQndiUExGdXlyc0s0ZHowTWNoUmxMcnVNeE9EQmFoR0hvdHlMNW5LdUNxVVE0TDFaZVFRblU3ZnQwOUwtY3Q4RmQtcnRzWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQNk9oVWZycVZaTy1oVlZoZl91VnE1U0tINURDVk1MeG0ydUNUMnY0dmJ2Tk1pc3h6ZTB6aGZ3UUpIRTF5dDQyenpMTzB3VDBfOUJJUVkzcWwzTFRBTUlSUEd5a2NsODZ0QUQ0VjZacC1BWnI3dVFNb3l0ejBVVk5HVGd2RjZEcng0LXlnT2pmcmExUVVlODFXUjB4akFKZnFBc19sRlpKcThZUmtpdTZCVS1EN3RzUW9rUDRyamZJWWh5QXlxRUR3dG5MTTNvWExVa1N6TnJSdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
+          <t>“Loira feita em laboratório”: Piovani detona Virginia de novo e fala em “cheiro de enxofre” - Jornal de Brasília</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>15/07/2026 16:02</t>
+          <t>15/07/2026 16:45</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNT1kzRjVZWWdPSDgwOGhBYXMtYk9ob0lyNUV6SFdCa3FuVkFYdlhxT1hFREc1N3V2R0lTa01qSFpnVXJNTlY4eGNudVdDenZlelZPY2lHcGlkV3lOYVgwVVo2aVVlcWRxZ2ZLelg3dW5nWmVERG94SlFZNXREaGZWaTN4RmN4dnRsRWtaT1J6ZmlUU190b1hWNlUtQndiUExGdXlyc0s0ZHowTWNoUmxMcnVNeE9EQmFoR0hvdHlMNW5LdUNxVVE0TDFaZVFRblU3ZnQwOUwtY3Q4RmQtcnRzWQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Luana Piovani ataca Virginia Fonseca na web e diz sentir "cheiro de enxofre" - RedeTV!</t>
+          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>15/07/2026 15:47</t>
+          <t>15/07/2026 16:02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeElPQURYRFNpd3kwclhTbnFRQTFOMzNTcGE0OHdZRDk0R1Q4bG1EbHg0aWw3cDRvUmdHZ0dsSFBWby1tbm5IYlhhWTVlVzNTa284QkFRZVpKd3dVbVNHb1NRTGhNbGppSW5OQktkTlR3azRGYURteVNxVnZvLU1lMDNmMmJCVmZKS1pKVnRJRHpTSVdyUXZDRWRCc0IwbjFjTEFOY2dBNkFfTFF5QlBaTTNhNU1Fb2JvRkl3VXZWUnJMVy1aZnNSQtIBzwFBVV95cUxPWjlYY3V2VXZsekpsaFBRSTR5RkdnSk93clNDS0NLdGdzeWd2ZnNMXzlvS0ZRS1UzT3FOOFV2TDdmYmhiWDFjdEpVTkVPMUdDVXFBQjdXRGZFeGdHZ3dOYU1qekFGSFl4aGFHNmZrSUNPSXBuRWctMWtGTGJRc2p2RExXd2NPN2xucy1tY21TNUstRE1nWi1IZDVtTGxEeTJLdFJnWWR6cmZXdVFTVEVQQk85QUE2cFRvVThCNU81dDY3Y3RidEwwQ054c0YtQlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
         </is>
       </c>
     </row>
@@ -1436,61 +1436,61 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>De "dinheiro de sangue" a "cheiro de enxofre": Atriz Luana Piovani volta a atacar apresentadora Virginia Fonseca - Cliquef5</t>
+          <t>Luana Piovani ataca Virginia Fonseca na web e diz sentir "cheiro de enxofre" - RedeTV!</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>15/07/2026 15:41</t>
+          <t>15/07/2026 15:47</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQd2VrMEdzaS1fNEhYcm1nRFlvQ1VvUzlubC1id0RPRWp4LWs2NFAtbEYtNm96M3dibUxhUXp0TEh3Ym9xU0YtNHJqUXhlQnE1ZkxsdHdQZ2dPTUNQb18zRWNFWHZHOFQ4SGZtNUM1TXYtUl9vQW9aOEJ0U0JGMl9CNl90RnowOWk1NWZfenFFd2pyTlRrOFU4Y0RoWXJhUjB0enl5djR0TGdUMWNCUzhiOHYwX0FRdWxjLTFyTjVZTnJmaVBoUkZncmpXZjA3cUpxQ2R6QkdNRE1NdmExYjZBNVVINXQzTkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeElPQURYRFNpd3kwclhTbnFRQTFOMzNTcGE0OHdZRDk0R1Q4bG1EbHg0aWw3cDRvUmdHZ0dsSFBWby1tbm5IYlhhWTVlVzNTa284QkFRZVpKd3dVbVNHb1NRTGhNbGppSW5OQktkTlR3azRGYURteVNxVnZvLU1lMDNmMmJCVmZKS1pKVnRJRHpTSVdyUXZDRWRCc0IwbjFjTEFOY2dBNkFfTFF5QlBaTTNhNU1Fb2JvRkl3VXZWUnJMVy1aZnNSQtIBzwFBVV95cUxPWjlYY3V2VXZsekpsaFBRSTR5RkdnSk93clNDS0NLdGdzeWd2ZnNMXzlvS0ZRS1UzT3FOOFV2TDdmYmhiWDFjdEpVTkVPMUdDVXFBQjdXRGZFeGdHZ3dOYU1qekFGSFl4aGFHNmZrSUNPSXBuRWctMWtGTGJRc2p2RExXd2NPN2xucy1tY21TNUstRE1nWi1IZDVtTGxEeTJLdFJnWWR6cmZXdVFTVEVQQk85QUE2cFRvVThCNU81dDY3Y3RidEwwQ054c0YtQlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
+          <t>De "dinheiro de sangue" a "cheiro de enxofre": Atriz Luana Piovani volta a atacar apresentadora Virginia Fonseca - Cliquef5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15/07/2026 15:16</t>
+          <t>15/07/2026 15:41</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQd2VrMEdzaS1fNEhYcm1nRFlvQ1VvUzlubC1id0RPRWp4LWs2NFAtbEYtNm96M3dibUxhUXp0TEh3Ym9xU0YtNHJqUXhlQnE1ZkxsdHdQZ2dPTUNQb18zRWNFWHZHOFQ4SGZtNUM1TXYtUl9vQW9aOEJ0U0JGMl9CNl90RnowOWk1NWZfenFFd2pyTlRrOFU4Y0RoWXJhUjB0enl5djR0TGdUMWNCUzhiOHYwX0FRdWxjLTFyTjVZTnJmaVBoUkZncmpXZjA3cUpxQ2R6QkdNRE1NdmExYjZBNVVINXQzTkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
+          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>15/07/2026 13:10</t>
+          <t>15/07/2026 15:16</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
         </is>
       </c>
     </row>
@@ -1502,17 +1502,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
+          <t>Luana Piovani volta a atacar Virginia Fonseca e dispara: ‘Sinto o cheiro de enxofre’ - CARAS Brasil</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>15/07/2026 12:35</t>
+          <t>15/07/2026 13:10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQcVBtVkxvbHluLV9INDQ1WXpUQmNnSjJ6OThtSkhMM2ZhVlBYWVRMMmI3Q2xZdE92dVlxVnd0ZTRkcEdPdHZaQVA0RmFrRjRuY0VsVTZEaVprTV9idS01dWZWRnFZMFltLWhubTU4OUVzYUhNOXhzQkVfM2R5QWRxLTVMUlA4Z2hvSlZ3RURVTjVvTXpsZ1M3RlVCOThQTlBfRzNxUW9lbW8wNlA3dmMwYzUwUTB2dXpZamtVMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
+          <t>Luana Piovani volta a atacar Virginia e a chama de 'loira de laboratório' que exala 'cheiro de enxofre' - Alô Alô Bahia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>15/07/2026 11:51</t>
+          <t>15/07/2026 12:35</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQZEd5VUtYUVlHZzFBYTllWkxLUlBGdzdmb0QwTzUybFJ0QTFBYVc2S3hnVERNblRNQTR3cktnMXFZNGFDUTUwLWVHdGZkMXJ5UTVoRFZVMnVvWmVYeURFeHRyazhJLWluc3JmUkJOTHRtRlZCZnpCQWxGRHplbTVIYUVfR3prLVYtUUtPSjdhMTJFRFQ3RVFUUEpqT3N4dkJEUWV4WVdXN1FQamdwZ3hqbUNtQzNQSVJKRjdKYlpXc3piRzRBUUhmM3FMQjQ1eGkyOHFUM3ZBWTExQlV5?oc=5</t>
         </is>
       </c>
     </row>
@@ -1546,17 +1546,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
+          <t>Polêmica sem fim! 'Loira feita em laboratório', dispara Luana Piovani em novo ataque a Virginia Fonseca; atriz critica envolvimento com casas de apostas: 'Sinto cheiro de enxofre' - purepeople.com.br</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>15/07/2026 11:09</t>
+          <t>15/07/2026 11:51</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOa3EzU19ScDlIRnpUUmxUVm1ucW92dTB6WkZjRGdYdTlFUEt5bkFmdDY0bWxjWm5zSXlKU0QwVC1PQy1SZmFvc2JhQjBzYTdiWkRYd2hWVjhTYk5yQ2hTNlFKenJCYndFMEhCMmxpaG9tLUQ2UDdFVEljY2UtRVdhQXhvV1huMUt3aExpYzFNSUlJUnNIMjQ1aFhfeTZ1TGRBSnVBMVIybmEteDdScXBlQS1VY2hGYk9MU2liY191QVROSE1ISkV3MnphMGpRSnVQSEhicGhXSVJFQ1JVMXctYUFlcVRxQi1kZmJJdndxUdIB9AFBVV95cUxQdmttVnh2MFFZVWozRTJFemFYblhweEtWZnVvbzZRNFJZVTF6UlAyeVkwLWVxdHZjWHA4MUFxVDlPNlpnQXVNOG5kZFZCTUZLZ0h5OTAwUDlqbXNGcmNubEE2TDNvbGRtaUJSTXh3eXNQTEpZZTFHbHA0Ry03aTdnRnFTdHA2SURrSUJmNVdLNkZWcDREQWV1QkVLcFI1N3kxWjhFWTdLRmltam5XSUp0NFdPSWQzRWNpcG12V1NIV0g5ZVh4Mk5ESnQxSXo1ekFfaTlDYjNGQ1l4QkthM0pfd1NyMXZjdG1Ha05qS3o0VG5GM0hY?oc=5</t>
         </is>
       </c>
     </row>
@@ -1568,17 +1568,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Luana Piovani volta a atacar Virginia, chama ela de 'loira de laboratório' e dispara: 'Sinto o cheiro de enxofre' - Globo</t>
+          <t>Crise no Oriente Médio já afeta o agro: falta de enxofre reduz produção de fertilizantes no Brasil - Portal PaNoRaMa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>15/07/2026 10:17</t>
+          <t>15/07/2026 11:09</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQkdPbWpjNnBsbm0zaUw5ZzEyUzd3R3hyOXlSZnEtMlpNS0wzZXAzbHpMSVhrSXV4VFcyakNvLWlnYnlwLVg0MjF3bnBJWXZuOG83TmZ6S1dKQlU5LTNUc0x3clZnMnNUV1pBbTB3UDB1djBzaEVxWWZaR014Mk9KS0tZMElTRkhCcjE4UWExNGxuMWhkUXVValpwUlg5UEstU0Q1ZElPRGxEZHllZXdvZ21nWdIBwgFBVV95cUxPRDNHYW50ZDRBR2JVSkRRbWhYTjhWYTd2SERLcUNvOTJIS3JUdHBTZC0zWUV5ek5peHlYNW5NWWVxWGo2emtYcUhjRGFiLXNmSHpQeUFvUnI0TG56YTh6Xzl0em1vM3pBQnZ2RWtJRTFRcGJiZm5LTVo5SzByUjh4TjZmdmRUa2tuX085cDRRVGJYSmtaOUgybEpEZlc4OWRnb2loVi1pRkQ4SDJqU3VveGpjQlkwdkdFRnAyTExYTklOUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcUhycC1KSVpwR01nZ0oyUEZwbGtHblZ0a3Q1Nmp4WjRhTURGYTJvMU9DcUdMUlpsNDBOSlhfX21LTk9mV3ZXUWZBWmFFaFFmcGFMYTQ2bWV6M1pYLXk2RFZZb1NPdHVhdmtBdTJtb0lOTkNRaTFPVUhMMFlOaFRFdVFwTnJxeFBRZEkzX0lGWWx4WnhHRVZHekpCZ1VBTVRVc2Q1c1FqUXdnLUhUX0txMXlJVkg4YWxw?oc=5</t>
         </is>
       </c>
     </row>
@@ -1590,171 +1590,171 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
+          <t>Luana Piovani volta a atacar Virginia, chama ela de 'loira de laboratório' e dispara: 'Sinto o cheiro de enxofre' - Globo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>15/07/2026 08:00</t>
+          <t>15/07/2026 10:17</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQQkdPbWpjNnBsbm0zaUw5ZzEyUzd3R3hyOXlSZnEtMlpNS0wzZXAzbHpMSVhrSXV4VFcyakNvLWlnYnlwLVg0MjF3bnBJWXZuOG83TmZ6S1dKQlU5LTNUc0x3clZnMnNUV1pBbTB3UDB1djBzaEVxWWZaR014Mk9KS0tZMElTRkhCcjE4UWExNGxuMWhkUXVValpwUlg5UEstU0Q1ZElPRGxEZHllZXdvZ21nWdIBwgFBVV95cUxPRDNHYW50ZDRBR2JVSkRRbWhYTjhWYTd2SERLcUNvOTJIS3JUdHBTZC0zWUV5ek5peHlYNW5NWWVxWGo2emtYcUhjRGFiLXNmSHpQeUFvUnI0TG56YTh6Xzl0em1vM3pBQnZ2RWtJRTFRcGJiZm5LTVo5SzByUjh4TjZmdmRUa2tuX085cDRRVGJYSmtaOUgybEpEZlc4OWRnb2loVi1pRkQ4SDJqU3VveGpjQlkwdkdFRnAyTExYTklOUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisações em fábricas no Brasil e EUA - GlobalFert</t>
+          <t>Eficiência do enxofre no solo ganha protagonismo no manejo agrícola brasileiro - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>14/07/2026 23:07</t>
+          <t>15/07/2026 08:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcXFEN1NxS0ZmN1BhczFiUVJSdGxEYWtnaUt3UzBneWtMdmthQV9lbHNMa25raml6SUpsVks2VXRrSkM0eW1DdXR6RW9QM25IM1RUck8zSmt2VmRkMkR5Y1FONG9HWTBqckpBRE9NVEJzeEs5Rk4xbEt6SkFSMHJWTE9mTmM0ZjF3MUNfZ1psNTJtR0dOODA0Um9DZTBnaTVTNGRRQWN6TnRPYUZNMG1iZVo1aXk1bXFjUlVVQ1BkakFVdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQSkZycWdLVDZKNm5qcVlpdEh5aVBvTGtGNWp5MzRPN2lxcXROR1VxanltZ29OdXY2SDNuTjA1Ym1RdFlYMGhXNlNVMF9ESzE4UFNfTDN4TzdSZnBFS3JaRE5ET3E1NVhjMUJPSG5ZYjR6VlFPNE4xUEN0RU1CaS1YRlQ3dUc1XzZnOGVtWUZGMkRobkVfMFN1R2pIcjlPZHlnbDlXbHpvY0QtV3RfTGo3ZGhRYnFfX3pnaVhoMkJ0NDh1Uk1HNXdjNmZNTmZkMlFCRXlpQ3drV3hZbUNlSEF3RXBpc0dOTzh1a3pv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Galeria de Flooring Panels - Dietfurt Limestone - 6 - ArchDaily en Español</t>
+          <t>Mosaic anuncia paralisações em fábricas no Brasil e EUA - GlobalFert</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>14/07/2026 22:11</t>
+          <t>14/07/2026 23:07</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOMy10V0pjLThwV1lNZEEwQTFNLUtxbGRYZU5ZT3ZJRm5Wclhtb3ZHTFQydXkyYkhtNlJxdGt2Wk52bXkzSWxKN3lCSzE4UUpTTTZyX3lVRXdwX1pSV1NUc19faFFjQjRGODhBc3phcHVmMGg4eTU3bHNMSjd3RFVqUTkySnhlYjRFUXFGM3ZqeEhLUTYwMlZnWDdUSkNjY1dQTldBSDJtcllqaFd3cDhhTXdjcHV0Q2lycUV0eHNvMkRNZFFZQnhLakhLQzVqQ2pYc19EWUE4bmk3YjNaUi0wOFFPa3duazFPN2k2SGh5NzFKUGpHdTJpa2tB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNcXFEN1NxS0ZmN1BhczFiUVJSdGxEYWtnaUt3UzBneWtMdmthQV9lbHNMa25raml6SUpsVks2VXRrSkM0eW1DdXR6RW9QM25IM1RUck8zSmt2VmRkMkR5Y1FONG9HWTBqckpBRE9NVEJzeEs5Rk4xbEt6SkFSMHJWTE9mTmM0ZjF3MUNfZ1psNTJtR0dOODA0Um9DZTBnaTVTNGRRQWN6TnRPYUZNMG1iZVo1aXk1bXFjUlVVQ1BkakFVdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
+          <t>Galeria de Flooring Panels - Dietfurt Limestone - 6 - ArchDaily en Español</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>14/07/2026 21:19</t>
+          <t>14/07/2026 22:11</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOMy10V0pjLThwV1lNZEEwQTFNLUtxbGRYZU5ZT3ZJRm5Wclhtb3ZHTFQydXkyYkhtNlJxdGt2Wk52bXkzSWxKN3lCSzE4UUpTTTZyX3lVRXdwX1pSV1NUc19faFFjQjRGODhBc3phcHVmMGg4eTU3bHNMSjd3RFVqUTkySnhlYjRFUXFGM3ZqeEhLUTYwMlZnWDdUSkNjY1dQTldBSDJtcllqaFd3cDhhTXdjcHV0Q2lycUV0eHNvMkRNZFFZQnhLakhLQzVqQ2pYc19EWUE4bmk3YjNaUi0wOFFPa3duazFPN2k2SGh5NzFKUGpHdTJpa2tB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 3 - ArchDaily</t>
+          <t>Deputado Neodi pede calcário para atender produtores do PA São Domingos, em Buritis - Ariquemes Online</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>14/07/2026 21:03</t>
+          <t>14/07/2026 21:19</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWDkxMWxDSjBFY05PdTVxUE5pZnVENF9kaUt3d25QNXI0dWJyLXZ6VUc3eHN5bHFaZ09kZnJYQkxqU2hKOU9Cd2ZDY0Z5TE5fNnFrbm1qUUNtNVo0dl91U1FPc2hzTTR1aVpaajB3Q1k4R1RUaXJpU3lId3E1bFA1Y1dkQlk4NDdFNTdWa0wzUFU2ZTU0VWdmb3BxOHhpTms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOM002b2tRTzBVQi1qWVB6SDR5d1M4eFppUzF1aDZXYVVTdUNIbmpMRmppNjU5am9pbjMxeXFsenlnekQwZ0lhczNXM3NKdHZzUHpBTGVodjl2OW9UVzZtX2QtaWNBb00wNGRLa0dnZkhyam1TQ204ZVVTRG9iTnZ2cExORkVwUDRHaTR0U0RPd1VZZzJPSnVJbkEybnhvWUdheFFJT3BwTkRQN0x5U1V0Sk5zSkdNZjJHUWtEVXZqY2RkS1ZMVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
+          <t>Galeria de Wall Covering &amp; Cladding - Dietfurt Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>14/07/2026 17:57</t>
+          <t>14/07/2026 21:03</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPWDkxMWxDSjBFY05PdTVxUE5pZnVENF9kaUt3d25QNXI0dWJyLXZ6VUc3eHN5bHFaZ09kZnJYQkxqU2hKOU9Cd2ZDY0Z5TE5fNnFrbm1qUUNtNVo0dl91U1FPc2hzTTR1aVpaajB3Q1k4R1RUaXJpU3lId3E1bFA1Y1dkQlk4NDdFNTdWa0wzUFU2ZTU0VWdmb3BxOHhpTms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
+          <t>Parceria investirá R$ 320 mil para pesquisa de solo na UEMS de Cassilândia - Midiamax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>14/07/2026 15:28</t>
+          <t>14/07/2026 17:57</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYml3VUVFMndVQl83VnhfUWVEaEtQYU8yajNNN2syUWxpMXktamtzRjlaalVNTGhlQkVwT0xZWU1wVmx1b2twRGdRSzNFRGNNOGc3VDhCRXh4VThheXRXNVUzeEVvU24xVkF2Qk9KbmpvVml0U3ZyQTJ6dTRZamtYSHNOUW9YVUNTUmtfSFVPbi1HM3FsTFRfOFIweF9ORU5F?oc=5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fertilizante em alerta - Olhar Direto</t>
+          <t>Passa Sete adquire distribuidor de calcário para fortalecer atendimento aos produtores rurais - radiosobradinho.com.br</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>14/07/2026 15:27</t>
+          <t>14/07/2026 15:28</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOQ2R3Y1NoTFE1U1NjTnNxUV9vWnJWcjV4WUxxX2ZJNWt6Q2dmLVI5N2RxT2Y0Ung2QXZQc0ZJakF1OXpBOVNTV0FhRjlXb1NXdDRSeVRiSm55SHo1bGsxR0R3SjJJbUdNN2VEcU1rU2t2dzhiVl9MMkNPMjQ1dDBLekhoNDh6cUlodU50UGNOZFQ2ZFViMlVoT1IxaF8xdnNRSE9fc0djWnV4Nmk2bnZuR1ZveWJCcFdOamZYWWg3REpNVTVRcVdtUA?oc=5</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
+          <t>Fertilizante em alerta - Olhar Direto</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>14/07/2026 15:20</t>
+          <t>14/07/2026 15:27</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYlAteXhKQmc0VXRFcE5jcWZGbkxlZzVJRXd2V3FiWHN3VkJfU2J3cFVZZVFRQ1dvSXZ4VE1VY0FjbS1EanN1c1ZXa1lMLU84RGx6cG1TTHdJNHR1UDEwYnZoV2pMREFmd3V5V0UyY3BuLVBQMnVNUEtqb0tFTGpKT0Z1S0RJeU5RZ1VFdF8tbXdPNTdMVFlQQzBVMldOZ3FOa3RRa053QXc4ZXNWWlcyWFk1YmI1a3lsVkFrZ1JDSFZKU1hMOHpENjltVUZrWUFYT1dEWGl6S2JKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1zY1FWdWlnSWxfY2tCYkR5M2Z6YmFhdWUza2tRRTRtQW9hUWFNRGs3N2FGSFU1ekdyUldESy1ESDlJOUhoZWcyZFVGSFpabkl0LUJnU1kwLXQ0MDNpUVNzTzF4eVUtUllSQzJjSllwS21Tems?oc=5</t>
         </is>
       </c>
     </row>
@@ -1788,17 +1788,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Guerra no Irão: Empresa de fertilizante Mosaic reduz produção no Brasil por falta de enxofre - MSN</t>
+          <t>Anvisa manda recolher lote de coco ralado ‘Casa de Mãe’, da marca Qualicoco, por excesso de enxofre - Estadão</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>14/07/2026 15:11</t>
+          <t>14/07/2026 15:20</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQNlFCMndnWHc2SmZlclVRSm4xMzA0bWlkUWxlWlFHaWt2dmVjWlpEWEFWTGpoNktGNnFGdVZ6Qy1BR1lpT2xoWW82b0JldGJWZnprZ0hVQTlIUUQwTFZ6dVBsaEg0RnJuMHRLeExoc0V1LTVHY0wycFJoLVlRR0ctbEt1STVteTZQZlhuQjhLajV3MlB4NDFJZ1QzemFqbV9UYzJIdEdIc2VhaTJpT3FZSnBxUkwtLUx3SUZQTE5zU3lENFgyY1pfWUtiT0pHalJXRE5JczhiZGtrVWFzaDE0QkdrdG9nUmVqS0NPRlZhdmVoSW9YWlRBNEJMQXdTLWJRaGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPYlAteXhKQmc0VXRFcE5jcWZGbkxlZzVJRXd2V3FiWHN3VkJfU2J3cFVZZVFRQ1dvSXZ4VE1VY0FjbS1EanN1c1ZXa1lMLU84RGx6cG1TTHdJNHR1UDEwYnZoV2pMREFmd3V5V0UyY3BuLVBQMnVNUEtqb0tFTGpKT0Z1S0RJeU5RZ1VFdF8tbXdPNTdMVFlQQzBVMldOZ3FOa3RRa053QXc4ZXNWWlcyWFk1YmI1a3lsVkFrZ1JDSFZKU1hMOHpENjltVUZrWUFYT1dEWGl6S2JKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec3bab247adac737658ff8cd917&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbad11b472396ea0e332a9f7670&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec24ca04f81b8794fa763fc1a7d&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbaf51c4b9abeeff07e3a4b2af8&amp;url=https%3a%2f%2fclickpetroleoegas.com.br%2finteligencia-artificial-decifra-as-regras-de-um-jogo-de-tabuleiro-romano-perdido-encontrado-em-uma-pedra-de-20-centimetros-na-holanda-flpc96%2f&amp;c=951759223804362979&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>11/07/2026 01:40</t>
+          <t>11/07/2026 04:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2817,88 +2817,88 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dados da importação de ureia em junho e expectativa de preço! - Farmnews</t>
+          <t>Crise global no fornecimento de enxofre afeta operações da Mosaic em Minas. Unidade de Uberaba entrará em hibernação. Entenda… - Jornal Araxá</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>10/07/2026 12:37</t>
+          <t>10/07/2026 08:50</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPaG9iU21CY05aUGR1OExxRUNPbGtmTGZVOUtISUxJUTY5QThsM0tfNkQyVWNuckN0ckVral9IR05uVThNUDVYOXhvaTVvclhlMzhtQzkyTC1jQnlGbE9iSVVKcDNZM0FOT01nTXBRVWJuVWdLNHR3Xzhvd09QSHZmRU1TcFppeFA2dE9sZzEweHdVOURTZ1JHTlJBRnlybUNlcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPbjdHT0tYWjY2TzhYZVNDT2JfVDZHYUdYMnQ0d3BWTlB0S3p2NGJzQXRwWlIxVVZJSHdFUkNJQ3FoMWZTcl8xZTBkdnM5QWRFaUo4REI0Szc5S1psZ0VVYXhSYUNOM1ZrZmpuWkV1NHVkVjJXRHU2SHJ1aTFlVFpXeW1felpCQTJzNkE2bzlJcG1iNmtwUC03TDh4UWNCTnM5cmp6VERkbEJZdmhQcU9kc2N3X1c3Y1Z1dGtZMjdYdmhhS1RGdzgweEQ5endrbkNGUnUwUzVya1RWQmJnWktZcUIwRXd2dw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Crise global no fornecimento de enxofre afeta operações da Mosaic em Minas. Unidade de Uberaba entrará em hibernação. Entenda… - Jornal Araxá</t>
+          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>10/07/2026 08:50</t>
+          <t>10/07/2026 08:32</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPbjdHT0tYWjY2TzhYZVNDT2JfVDZHYUdYMnQ0d3BWTlB0S3p2NGJzQXRwWlIxVVZJSHdFUkNJQ3FoMWZTcl8xZTBkdnM5QWRFaUo4REI0Szc5S1psZ0VVYXhSYUNOM1ZrZmpuWkV1NHVkVjJXRHU2SHJ1aTFlVFpXeW1felpCQTJzNkE2bzlJcG1iNmtwUC03TDh4UWNCTnM5cmp6VERkbEJZdmhQcU9kc2N3X1c3Y1Z1dGtZMjdYdmhhS1RGdzgweEQ5endrbkNGUnUwUzVya1RWQmJnWktZcUIwRXd2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>"Calcário convencional: herança do passado, desafios do futuro" - Revista Attalea Agronegócios</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>10/07/2026 08:32</t>
+          <t>10/07/2026 05:34</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQRXBKODRUMjRqNVVvbmlITmlfVVNET045UHpPY0FoeldGMU5QZXRDdE9YTDU1WExQcXBOUHRTUlVoek1xUjc2NGxwVVhCcjNTV2t4RDlZZFBkY3l3OGZfZDZYNnFCczJ1b25MTmpmMGQ1MkwwVnBISmNOX25jd3BNRnI0NEJMU2ZZVlEtZTVCejlOSFlDdXBDc3dxaEtycEFaSUdwSE00MHhHQWZZQWZGdk5kTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - brasilagro.com.br</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>10/07/2026 05:34</t>
+          <t>10/07/2026 04:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWjlvdWJTZGZFS0lpRFVleTl2bDV3WWlrazRpXzhuaXp2ZzRtWEUwcVh5dE02VldqaDlza0t2QnB4SXBuV29WVnY2Ti10MF9WN3NhaXViUk4zeXI5YkpUZWpHYWtuOUxsQV8xM2hrN05Edm5OaVMtMXlxT0NON2VYM3F4ek9BTjZ6bWQwS3l6aHF0NzlfMmttd0FqY0pFR0VRRWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2942,85 +2942,85 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
+          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>10/07/2026 04:00</t>
+          <t>09/07/2026 18:17</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Mineradora CMOC firma acordo de R$ 11 milhões por contaminação do solo em Catalão - Tribuna do Planalto</t>
+          <t>Prefeitura de Chuvisca define distribuição de ureia para produtores de leite - Portal ClicR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>09/07/2026 18:17</t>
+          <t>09/07/2026 13:46</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPNVpiSFpMWmIxLXpEWVZOeElNOHlkZ2JZX3c5dzRFd3otN2JCYm96blhvUjd6N09MeVh3U2ZRY09OekVrcEFMcXZGM0xGY0RTTHdPNVVJVWc3aXRnZ3FyZDlQNElsc3hoWktUMTdSNk5KWWtvcnJHN0E1MWZ2aWFLalRwdUZIZzdwVzV5TTFrVEN5SFM4djNjQWVpdVBYTzNLY2NhU1ZQQ2FHSW80UUxNb2xkOHY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdHRaa3pPRVdoSzFsWGJiZElFNEc3QTFhYmpEX1Z1bC1uNk1uQXhqM2Nld2kwTGtqNlBsVTdaZXpBbGdia2xqODlMNU52NlRNaTVsWDl6dG52ek9WQ3dPLVBMS0c2eTNsUUVHUmx1RERiRUVnTXk5dC15X2ttYmxIRmx2VXBjS20waGJJeWFUS1ZTdHJMcGJ0ZHB6M01GcGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Prefeitura de Chuvisca define distribuição de ureia para produtores de leite - Portal ClicR</t>
+          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>09/07/2026 13:46</t>
+          <t>09/07/2026 11:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNdHRaa3pPRVdoSzFsWGJiZElFNEc3QTFhYmpEX1Z1bC1uNk1uQXhqM2Nld2kwTGtqNlBsVTdaZXpBbGdia2xqODlMNU52NlRNaTVsWDl6dG52ek9WQ3dPLVBMS0c2eTNsUUVHUmx1RERiRUVnTXk5dC15X2ttYmxIRmx2VXBjS20waGJJeWFUS1ZTdHJMcGJ0ZHB6M01GcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MPGO celebra acordos com a CMOC Brasil e garante R$ 11 milhões para reparação ambiental em Catalão - Diante do Fato Catalão</t>
+          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPaGNaUEY5c3pNTFRRejZjcy1ON21QYXRNMlVWbTFncHdWMHNnR2k3Y1NnbUxveVEyWXVzY21wemxMSUJoWTNXdmFGZWczV043QW15WkhKUGJjbFc3SF9JczE4OXNabzRPR3FYWEJXNExISmdRMDJ5R0dkSEZSVmJhZElhZF9tclZKVHpkV3dSdFAzMTVJaFR6eG5haEowNWo4LVFGbmtoMld1cEtKTFMxZ1REVDYyWjVwLUZtUWZFT281R2p6Y1RhcWVYVjNxcVIwSWxZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3042,83 +3042,83 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Mosaic suspende fábrica de fertilizantes e demite 30 funcionários na Bahia - BPMoney</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>09/07/2026 11:00</t>
+          <t>09/07/2026 10:56</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNd191NWgya3M1Mi1KV19TX2x4VnN5a1QtZXJ4Mmcta2NyVEFQajVPNnlMVTBUWTdfNFpORFdsb21KYnZNNlc2MU9WdWdZWWxybm9JeEllY2V4V2hiaTdlMDBNUV9pRVd5Umd6a25TSnU3b0E0cDZVZVRVb0ItNERObUpxczNvWUszbmI4cExUVFlMNUs2SDZfeHNfYnVoQ091MmZvWTVHTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - CompreRural</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>09/07/2026 10:56</t>
+          <t>09/07/2026 06:50</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNYmd5aEw0ajhQRGtrcXUxdG1JN2gxeWZVYTZsS1VVTGk4cnBEbThDNzY4WndKQVhONjk5WmhGUi1YNmtxek1fM1dRNmluc0VxOUtJc2xYQ2tCYjhuSnVCLTBnZXc0b3YwUUhpcWp5MkpLTWVTa2lwVjZ4eENrbWdrYXZFakpBYVVvaFRybDNXcXRTbkVJRVpxbUJMRUJXU0JTYzV3RzZsc050WlNOeXhGc0xaYnVaUHV3b3k0Mw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Luiz Armando Costa</t>
+          <t>Pare de jogar as cinzas no lixo: saiba como usar esse pó como um reforço natural para suas plantas e canteiros</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>09/07/2026 06:50</t>
+          <t>09/07/2026 06:15</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQMWpueTF3aVVYMWVnUU5aWHduSWUyZy1jNzBCWXlLZl9qQ3pTMnY0MmFhY2twNXk4V0ZaNy1oU0c3SHlrZi1KTV9pVUhvdW5EVnl1MnJEaHB0UF9rVTcwTnhCLWcwM0N6cTFSUEhfUHBscDF6WTRZcDFFUFk5R2ZxaDJmQ3FGUHgyQUF2RDJnWURZRm5EdWYzTDI4aGphekttRjY1Zm5POTFqc2lhWTdoTWxDYUo4QnpLbkpZN3lGLVY4dFVIRVVIYXRwaEp4YUhuT1BWOWw4WDJTTVc0X1Jvc1NfVjlST0NR?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbad11b472396ea0e332a9f7670&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pare de jogar as cinzas no lixo: saiba como usar esse pó como um reforço natural para suas plantas e canteiros</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>09/07/2026 06:15</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec3bab247adac737658ff8cd917&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil; fábrica em Candeias é desativada - Bahia Notícias</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQZDVsUG9Xc0YzNTVTYTJBQTVrWDk3R19HSWdJYVBqSUtNY0dTY1phT0dDZTU4NkkzZFNQR0c3UFQwMnFabVN6UFRLWFIzcFBWWm5KXy1WU2E2S3FUSWtYdEZ0Ukw2OThnMnBQeGtLNm5MS3V3QmdxSGZwQUhDYVRrS0FLZDM1UktSTlRFbnpON1Bya2ZLZ1htYzNQSzBqeVd2eC11LWlDY1R0elB0UFZTZ2JyanFHandkLV9HeTVvb2JFTlB6QThoY0ItWVk4b1JzSGZxRnYyV0lOeUhIM08zcUZyM2VRZFZPejUybnJWZGlYcDhQd0ExdVdIbE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3196,17 +3196,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>08/07/2026 20:25</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
@@ -3218,83 +3218,83 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>08/07/2026 20:25</t>
+          <t>08/07/2026 18:08</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
+          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>08/07/2026 18:08</t>
+          <t>08/07/2026 14:33</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mais de 500 agricultores de Palmas começam a receber calcário para aumentar a produção rural - jornalprimeirapaginato.com</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/07/2026 14:33</t>
+          <t>08/07/2026 11:07</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPSUVMcFY2WlNBZFJRbTZZX0dwbnAwZldlb0xfYnk4WTVfYUZWdmJxc2FCR2JFV3hLWTQtM01OWHJDX3BLTkhRcmNjTEdtUHBXWG9SYXJjVjZOa0pmWEJMekphSGlUMWkwNUFlYjBKZnlGbE4zaHplY0tFQzRMZTRHQlQyeGJZLWZKVU03UWNTd3dRODljMnRsUng0WWpHM2FydUI5dFpOVHJZa1ZaM0J3WW43cWNwSjd2Z05pLVY0SHVGRnlaN28w0gHMAUFVX3lxTE9nWFU2bHF0dEQyV2M2TXFNX0dnYVBySlB5aUJIcVF6Qnl1bk5QM3J6SHVPR3hqbS1iQzJkTkRQdlFabG1Ienk2SDRIZDNNS3dwd2FCVzFKLUg5cmh3Njl6WndDZUh2QXRXYzI5ZzJPa21tSFVtM0otZDNxSWRMYkR2OS10TkNvRWtuS25yQVprU0hlZFk4TG5GQVRMTlpYRUdGUjVQN0xjaGFyMTZFZFp4VV9TVEtrRk9kMUZGblc1aUV0V0poZTFlUWFXZQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcc07e6a40ef8a14007cc5c80b86&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>08/07/2026 11:07</t>
+          <t>08/07/2026 10:03</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec8a7724bd182aaa939270977a4&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3306,83 +3306,83 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura Municipal de Sorriso</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>08/07/2026 10:03</t>
+          <t>08/07/2026 09:54</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - Prefeitura Municipal de Sorriso</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>08/07/2026 09:54</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>07/07/2026 08:15</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PACAEMBU: AGROPAC AGROPECUÁRIA é referência no fornecimento de calcário e gesso agrícola - Folha Regional - folharegionalnet.com.br</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - notícia marajó</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>07/07/2026 08:15</t>
+          <t>07/07/2026 06:18</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQRXh4dEJPWk80V3JGOWM2MS1NS1VIbWpWSVJYTENyd2lEX2FBYjRlMEZmYWdxdkNRa3lJU09lSVJBUElxU3Z0T0o2S1pDLVZTOGl6cjd3LWR5NjdDWXJlUGFCZUZrU0ZTR25FWkFqOVlpMDlSeUNPQzg0ajUxRWxNYVVId1NUS0ZTeVo4Szd0WC1WSmt5UTV1UUw4aGt6UVFfaWZLZFVraU1qNHFFTUFGa3R0c0N4aE9PNjlQVUJwZkZlaVY3c0xVMmNKb9IB0AFBVV95cUxPX0hTa0M5REc2M1hFa1ZDRm9xM0JSWjVjdGhJVUVwZUdSRC10M2owbWZpSFBZZHhpQVdMajFPWG1tdzFLS3hFN2FXazZBb1VDell2VVVqYkxwWXZobUdvenRHX1FsWEhyNEhkUFdvNW52NjY0OFJWajBtT1V6c2RadVdqNzc2TEZrRWd3cGVwV19xeGk5QzZubFF5WHN6bnVZYVNtQk5fRkpYNFNzNUpNN1dUWTd2MXFZN2gtQmVBbFdUNGh4a1NIQkZ5X1I4UTlu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQamJYM082OHV1bmtldUhFVXR2ZTB0LXNmd21QMWZucllOMlVRaVhueFA3dWgtM2dlY2REcjFKLXdMU05PZGgwNFhkZm5WOTJiTDBlUjBNLXptd05fR0xDYzgtTExpTk51R2VVM3piU21IQ3N3RlJPUFJlWE92TFVpWEJzSDlhMGRMQ2MwanVNT05vM3B1VENXUHJKdjlhZ3BJNFZZSkdLd0U2dTZvSzh1T2EzaUExbmYxN2NDZFVfYUNIS1E1eDl0WUY3eks?oc=5</t>
         </is>
       </c>
     </row>
@@ -3394,29 +3394,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - notícia marajó</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>07/07/2026 06:18</t>
+          <t>07/07/2026 04:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQamJYM082OHV1bmtldUhFVXR2ZTB0LXNmd21QMWZucllOMlVRaVhueFA3dWgtM2dlY2REcjFKLXdMU05PZGgwNFhkZm5WOTJiTDBlUjBNLXptd05fR0xDYzgtTExpTk51R2VVM3piU21IQ3N3RlJPUFJlWE92TFVpWEJzSDlhMGRMQ2MwanVNT05vM3B1VENXUHJKdjlhZ3BJNFZZSkdLd0U2dTZvSzh1T2EzaUExbmYxN2NDZFVfYUNIS1E1eDl0WUY3eks?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>ANM notifica CODEMIG e Mosaic Fertilizantes sobre dívida de R$ 55 mi de CFEM - atlaspublico.com.br</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3426,29 +3426,29 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOM1dxN01qNjc0ZDR6UXlRX2FsWUt0ZWxhcHExOGVoWDhTazJOdzBTUkpuandqc2szc2dhdzhhTUJlV0p6NGl4Z3MyanMtS0Y3czIwcUFFOXI5Q0U3NlQ4NWRRRW5Bb0NiMlF0aGhqRW13ZE5TbU9xcS02cmVwX1p6Z0hIWDRIQVNQRy1hcWktdXZUZ1psdWlYaFQ1ZFJGS013dERKUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ANM notifica CODEMIG e Mosaic Fertilizantes sobre dívida de R$ 55 mi de CFEM - atlaspublico.com.br</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Estação Livre MT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>07/07/2026 04:00</t>
+          <t>06/07/2026 21:29</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOM1dxN01qNjc0ZDR6UXlRX2FsWUt0ZWxhcHExOGVoWDhTazJOdzBTUkpuandqc2szc2dhdzhhTUJlV0p6NGl4Z3MyanMtS0Y3czIwcUFFOXI5Q0U3NlQ4NWRRRW5Bb0NiMlF0aGhqRW13ZE5TbU9xcS02cmVwX1p6Z0hIWDRIQVNQRy1hcWktdXZUZ1psdWlYaFQ1ZFJGS013dERKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWmFLanBDd0hKMG16cUM5MXJBRXJuc2dENlpiQ254SGN0ZS1rYXJQNXl5ZV95cm9oeDAxc0FzY3NwekZqMnkwNjBmSzRvYjc5NXkxcDVSUTRGZjV5bFVVbVpQOE94SU1wQmoyR1c2ZkhUdTRaQ2ctSEhxQUtsRzBKeG9FRWtwNVhlRVRnQ1FyS2dXNUx6ZGRPNlJ4VXZidVRKQ3BBWGI0UGhpN3paSDF6d2xjNUdmYy1OWXItUkpB?oc=5</t>
         </is>
       </c>
     </row>
@@ -3460,39 +3460,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Estação Livre MT</t>
+          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>06/07/2026 21:29</t>
+          <t>06/07/2026 19:20</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNWmFLanBDd0hKMG16cUM5MXJBRXJuc2dENlpiQ254SGN0ZS1rYXJQNXl5ZV95cm9oeDAxc0FzY3NwekZqMnkwNjBmSzRvYjc5NXkxcDVSUTRGZjV5bFVVbVpQOE94SU1wQmoyR1c2ZkhUdTRaQ2ctSEhxQUtsRzBKeG9FRWtwNVhlRVRnQ1FyS2dXNUx6ZGRPNlJ4VXZidVRKQ3BBWGI0UGhpN3paSDF6d2xjNUdmYy1OWXItUkpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOSkQ1Q3FXZnhQcXhNSGVzSjlFNWVKMmNCdzk5Q1hZTFdmeE5BOVg2YXIxMDUyYVc3S1g3X2dTcmJqcEZzUUctS2RpNGdPZVN3a2xZNUhzNTBlQjNfdU45QVdta0R1NDl3MzdrdGtFR1QyNnUtV1JNMElHaU1ycnI2UGhBVzJ6NDdqREVFSVNBS2ljM2RwNlF0OFdIelUwcVVEeWYwMEZZSGswN3dOdi1LNHZVVTlqWjI3NS1qUTNRX1BIMzhVc1RPRkROcE5jQThpVmxZRVJYV3hJUVlHLVZ0RGRBdTlkOGxsOTljUkpLNlV4eGNlbTlOTGppejZwZTRRR3JQR2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Preço dos fertilizantes sobe acima da inflação desde 2016 e ureia acumula alta real de 149% - Portal do Agronegócio</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>06/07/2026 19:20</t>
+          <t>06/07/2026 10:47</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxOSkQ1Q3FXZnhQcXhNSGVzSjlFNWVKMmNCdzk5Q1hZTFdmeE5BOVg2YXIxMDUyYVc3S1g3X2dTcmJqcEZzUUctS2RpNGdPZVN3a2xZNUhzNTBlQjNfdU45QVdta0R1NDl3MzdrdGtFR1QyNnUtV1JNMElHaU1ycnI2UGhBVzJ6NDdqREVFSVNBS2ljM2RwNlF0OFdIelUwcVVEeWYwMEZZSGswN3dOdi1LNHZVVTlqWjI3NS1qUTNRX1BIMzhVc1RPRkROcE5jQThpVmxZRVJYV3hJUVlHLVZ0RGRBdTlkOGxsOTljUkpLNlV4eGNlbTlOTGppejZwZTRRR3JQR2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3504,127 +3504,127 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Adolescentes de Enxofre - Minecraft</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>06/07/2026 10:47</t>
+          <t>06/07/2026 06:03</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Adolescentes de Enxofre - Minecraft</t>
+          <t>Importações de ureia recuam 32% no semestre - Agrolink</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>06/07/2026 06:03</t>
+          <t>06/07/2026 04:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQMlh1NlJuV2FMN3hicE42dEJqc01iSTM1endySVlqQ0kzaW1VVkhIN1l5UnNJXzlaenZhQW1WZFFnYVV5WlZTR2VjX2x2WGVUTzB6V1lUd1dXT1ZnYnYzQ056UmdjZUZCYm04bS1GXzgyQThXWUd6Nlk3VUFvazhsODhYQkU0UGNmT1pCM3NtcWVvakJCZ2ZsVzlJVFlERjhtQUd3NkZnZVNYVDhWc1F1Q3BOZjN4TzJZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNT0NWVXVuUHBIWmI4SlpmRGZ1Ujk5ek9GRjNHSkcxb2EwY1Y2ZGhPOFJnd1FLSi1yc21tZTFvTUwyWnZ1b0JhNlEyTDh3UFdOdnR2UjU4WDU3STR5eGx2OGMxTUZRUlkxVU9FdW03czY3X01WaWZLLUQ2QkNLVDU0cVFvTVBIeUMtZkVGaS1sN01wQ2pKRHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Importações de ureia recuam 32% no semestre - Agrolink</t>
+          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>06/07/2026 04:00</t>
+          <t>04/07/2026 04:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNT0NWVXVuUHBIWmI4SlpmRGZ1Ujk5ek9GRjNHSkcxb2EwY1Y2ZGhPOFJnd1FLSi1yc21tZTFvTUwyWnZ1b0JhNlEyTDh3UFdOdnR2UjU4WDU3STR5eGx2OGMxTUZRUlkxVU9FdW03czY3X01WaWZLLUQ2QkNLVDU0cVFvTVBIeUMtZkVGaS1sN01wQ2pKRHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes vê risco de desabastecimento de fosfatados - The AgriBiz</t>
+          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>04/07/2026 04:00</t>
+          <t>04/07/2026 01:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOODkwV0JUTEVFNC1zb3BwS1U5dE1jV2dDNG1DWkFqMGl5ZVVROWIzLXBfRlotcTNzOXRuYTdpZlNwNlpOQlM5aVRxdUtVT1ZYcjhpREhfX3M3dTdITlQ3RGdZdlh0WXVDaGs0S2xUSjJPd0xyYzZjUF9hQ1llTnpZUTJuSkY2a3lONXFsckxWam9ocW5yNXQ0VnRjWmRpTW5LNzhuZl9TLUxhdl9YQjJiRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>04/07/2026 01:00</t>
+          <t>03/07/2026 10:20</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>03/07/2026 10:20</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Reunião discute impactos da alta do enxofre na produção de fertilizantes em Araxá - G1</t>
+          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3668,29 +3668,29 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxPRUhiM29mNExlZUhDdUJFWkZCbHdOWkhNdURDeGV6MHREOE5XZVI2eWc5ZnBOZGNvS19SVzhsbFpFTWxlNGJwWkhyY3NGSDk2VnZLZ3Z0OVFydHFHb2twRnNVMDNxTTFZNVFNbmV2N0VqS3JFd05wTE9ucmRWS2FqS0hubWZlTnl3bkNhWko3TkNlZVRZQl8zNHJsb1E3RDF5VlNhS1FJR3hDcXBJMmtUaGdFSnB3T2RlZE14LVJINFdxaC1ZSFl2OTJ1MnliZjJKaEVlVVhwODd5a2U5ZUkxakZyMko4ZHV3UTM3aXI3SWRDRVlUaFRpcdIBhwJBVV95cUxOc09ockNBcUF5UGlBdDl1aktqUHhUYmItX3BOR1d6VXBHLUk4UFVuUWpvOWUxZWVMek1zTVd4V21saFpHY1dTbzFYOHNOVThEd1kxWVhtZ2lDSmRiemZMN3RGT0luOHlCQ081N1BTOGhydGdzbU9MUzlQMndNMWxSeDhEUGZaM2xrRGJkZ1JiT2NIcTVjV0RVRFhlNFNScHlXMmZnYXBGRExPcmlKODNSYjVHaGhaVnNXalJndnRsN0JCYWxPbjRKSlVBWU45TGxraURyMFUzRDFnOFAyLWI0VWRFcjdkN2tucVgxS2x0WHlJZW1kaHp1TkZpUGVMODJWU0ljdVV5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Alta do enxofre afeta produção e gera demissões em Araxá - G1</t>
+          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>03/07/2026 04:00</t>
+          <t>02/07/2026 17:01</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPdDlyUTJPY3lkTzRodWhvRVhRTjB1RHlEX2lGcWJxcHFQQlRjamRIY0VIYnhjWlVXVjFWQmtYOTQtSGhsU0NYbGZmSjVYX0Z0NVJXdEVfNzM2OHQwQl9uRG5oUElfbUtjblNEMl9VWWJQUTdoTEVFYkhnZWxNTFpHR1NOVm9TTU12eE1xR3pjak95YkFzWHpNN3ZKUmFvdjZEaFk3MkwxNXhMb1NLSTFaUDdJUlk5MWlpdW1OYnNuMkhZYzQ1cDQtRkd6cnMza0xNbHRQRHg3ZW5NbmVENjNaeUpQN1JOVUnSAfYBQVVfeXFMT1B5bkdkT0s0YXRtRzF5RS1pNDFXQTlLZHhrQnVZbU5RM3V2R2J2UW81a3NQOE8zd1VBcmtFbUNiRnlPaDA3LTlIT25DZ3dhOE9wRksxRXE5eEJaV2xLSVZ4OFowMFN5SzF3OU4tajdDdjFfVEFvZTFXVDl2dmdQZHVHd1drUjdOOVc4TlhDZmhhT0h6RmlWQ1M2ckxJMGxPWXZFVUl5WnJudzJIM2NoWkhUa3ptb1pGVUszN0RjRGN2TjN4aExoV202enh1OEdYOWJRdmhhTldhcFAxeHFydnFPU2VFXzdCblVIYmJnSWoxOXRCaEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
         </is>
       </c>
     </row>
@@ -3702,83 +3702,83 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Pampa Energía avalia construir planta de ureia para atender o Brasil - Revista O Empreiteiro</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>02/07/2026 17:01</t>
+          <t>02/07/2026 04:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1xQS16X1g0QnF4SGdXWE05VHVtSGxieGNYYzBFbmh0M2U3S3BKbC12cmFMekR1SlRVd1U1VEh5aS1SazFwQTI1TjdEYWhOYXFTRm5nQldUTGdUaFpHQzJseDNYN1pIZGJJVEdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>02/07/2026 04:00</t>
+          <t>01/07/2026 10:48</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>01/07/2026 10:48</t>
+          <t>30/06/2026 18:22</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>30/06/2026 18:22</t>
+          <t>30/06/2026 04:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3829,22 +3829,22 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>30/06/2026 04:00</t>
+          <t>29/06/2026 08:22</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3878,29 +3878,29 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Martin Marietta confirma acordo de US$ 13,5 bilhões pela Lhoist North America - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>29/06/2026 08:22</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNYUJCZDhUVml3MGVqMUw2QllsRmVrTF90WjJCYjhGUEtuVlVpc2hRNzJ6UzhJaDd3a1lnU0MtYnFGUGU4SmxNb1Jwc0hpZnJubUpVQ1U3UjhGYkk2a2VtRFg0Vl9mYWt4aXIxYV9xZF9SM29OcFhPdUJaVWVMQlcxcERTay1YODdGaVNMT2owWWdYeWNEWW5KbHk1Q19sTllKMng2T1lNNTBTZFAxRW5nV1pid2tZNnRzejJCc3M3SURsdGFXQnJGazhZRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Com foco em data centers, Martin Marietta acerta compra de fornecedora de minerais por US$ 13,5 bi - Valor Econômico</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3910,29 +3910,29 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxOQmNERDdXd2o0VlYxZXE2aDRFUV90bEdkWTd6ZUwyNjhJMDZBV20xbWxWZ2V6VGVtZG83VHFjSnVDU3ppbUZpTm1tY3NSWUNmRFhxeW5VaEp2SHp3c1BjVkxQZXBNZEhrd2RUdHVKZUNFTHlHZFliODlHMHp4c3lMbXhVUkhqWjltOFRzUVlJMU9Da0RIZnk2Y3B6bUVTelRSZ2tUT0c1aFVZamlSTERiX2ZIa1puUnVrUlQ1aDhtRW1uLVBZZ0NSSU91RGpPY243OWVLOXp3TGNjU0pKR015dFQ2RGI1dDdO0gH3AUFVX3lxTE1jZVlGVWNwdWlxX2lGVGpRTnRPUXJJNTJWbXJTcXRjb3lQQVFNT3A5TVhPM2xpSmRNOVZKZmFFR3Y5eEJnRlRNX0taNmppMTdVT1dBeDRKVjQ2TzNPZHR0OEhBRWlmM3VBaWcwQjVzSDZmM1hVNmJTcVVRR1VGYzkxY2trZ3FXMjNpNzlnUkRxLXB6UG0xbVBFZmU5MVVIa3FVZkdSMFFwaGhBeGZna01zOVNwUGFKMXpQdkstaWhud1RxVEJXUXVFdmt1bXdjNHF3azh6Vi0zSG1tbzE0aHQwaUFUNjNwdXVRNUdOaWlJeFVXTmZTSXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3944,29 +3944,29 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>28/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
+          <t>Brasil se vê diante de encruzilhada com fertilizantes - NeoFeed</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3976,19 +3976,19 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZU0zLWNfX1lNMUxiZlZlLVpPT0VUWDQyWXdlelBtQVI5azczdzY2YWw1TDJ6Z1Q2V2t3OXh6VFAtZk12d29Ddm5iWURjYUtFSVNzUERzZHZaR2xybzEyRmdNR3lVX3RiNTJGTzdxdTd6NTFxc0UzX1c0bjdGQklQWE4tZVl6SWtuRkN0R0JTbw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Brasil se vê diante de encruzilhada com fertilizantes - NeoFeed</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQZU0zLWNfX1lNMUxiZlZlLVpPT0VUWDQyWXdlelBtQVI5azczdzY2YWw1TDJ6Z1Q2V2t3OXh6VFAtZk12d29Ddm5iWURjYUtFSVNzUERzZHZaR2xybzEyRmdNR3lVX3RiNTJGTzdxdTd6NTFxc0UzX1c0bjdGQklQWE4tZVl6SWtuRkN0R0JTbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações - Globo Rural</t>
+          <t>Embarques de fertilizantes crescem após acordo no estreito de Ormuz - CNN Brasil</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4020,29 +4020,29 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNWDFOU0tpUTJqVVQxcEVDUmRCQXB2Sm95SXJwZlIyVkNxVmMxM3FpY0xVbnZxR3IyZkNFZE9NS3VOenZGYjVZcEUxN3hWOVJkNG51SGNhemc1TVQ4YWlLNEE1SFl6eVNjaWtZVnltMG4wU2VYTEZCMFI3Y21mZVBjNTBvSHE5eXlGR0dkQzFCVG5LTTBzOWdXRnJhM1dSV2hiQkJhNFFzajhwRTdlSXVzWV9MTDZiZ3RMSW9jbmxZYW_SAc8BQVVfeXFMT0l2YXdPMW5WTVN1OHFpQWNBekR5R0dKX1Y4WkY5dEtVbFdKVHJDMm9hV1lTY2FsQnFsVG92d2RuM0V1cGNCUmhYZHZjdzFzVlNkckxKaDhnVm9PUVNYRnJBaEt4WG5NVDloSWhLbEFZQmdXSWhqdFNzRU1ySDBHdmRYUlZZTDd0UzI3d3lzSm5ZRTM0Y2NCWnVMaU9WWElKa0pBZjlPUk5yS1ZhLV9Nd3FDRHVxMVF2bUVTWFprQTYwc2hpa3YtRzhKVi1hQUtr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOcENnZnlBVWF1ZEVFeElfLU56Y1RaZ2ZiQkdOck1KdnJkbzUwa1Z3dUo3aTItQmJrRjNKVVZKLW9NNHdhSE9FejZXb3ZiMDZZSTBGdk16SmZ2ckd1UHB2TXlNYnFZc1c2V0hlaXF4ZEpRT1pWcktSM055QXBtS3d2bVMtU1BFWkRkQmt6alZiYWFldVR0ZWp1N2hGMjRFLUlnMkxNTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>25/06/2026 04:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4093,56 +4093,56 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>25/06/2026 04:00</t>
+          <t>24/06/2026 15:03</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>24/06/2026 15:03</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Petrobras estuda duplicar capacidade de fábricas de fertilizantes no país - Globo Rural</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWi1PLVBielhUd2xVcUIxTFN2aS1PdWtOU1NTRnZ5UVNkQWtiZlIzeDVjdk5CUWZHSkltYlNiNFFCNl8wR1pNWklDM2VXOW5wOFdoNUxHeEdLMlUwbkhlTm5QaXJpLW1xQ3pJNTM5d0Q5NnlyM240dlc5QTVGcnhvRXBGWGtxaDZXSVlpdEVSZ2hBN2xLRzF3X0djZWtqLWFzQXE1WXZNU1Y3Skl1Q056RlV5QU1ESllnYlNRZGhTRkFQTFVIT0plbW0zTzLSAdsBQVVfeXFMTkNFR3VPQUJZS1IxMHBrUUN6UXVZMDJFb2NQOVlQMG9jZGRzTmstRDhmbi12ZGFhblRaSnVFT2tGSUg5RGNSZG9tMkhYUnBhOUJvMHJHQWZqNW5hVU9nUm5zMkZtVWpVUzJWWDMyWW94eVFaSG5MNEpxVVhOSEZIekZ1Y19IeXZwX2FCZjBCcTZjZElDcWUxM25FV2xDUXBnV0FGSkZNZ3dzMlpLNl9tdTVqdVlPWEJWS2RDN1dNeHl2Q2ZJOGtJWVprWDFBdXF5Mno0LTFGTUdlUWlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4174,19 +4174,19 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Petrobras estuda duplicar capacidade de fábricas de fertilizantes no país - Globo Rural</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4196,41 +4196,41 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWi1PLVBielhUd2xVcUIxTFN2aS1PdWtOU1NTRnZ5UVNkQWtiZlIzeDVjdk5CUWZHSkltYlNiNFFCNl8wR1pNWklDM2VXOW5wOFdoNUxHeEdLMlUwbkhlTm5QaXJpLW1xQ3pJNTM5d0Q5NnlyM240dlc5QTVGcnhvRXBGWGtxaDZXSVlpdEVSZ2hBN2xLRzF3X0djZWtqLWFzQXE1WXZNU1Y3Skl1Q056RlV5QU1ESllnYlNRZGhTRkFQTFVIT0plbW0zTzLSAdsBQVVfeXFMTkNFR3VPQUJZS1IxMHBrUUN6UXVZMDJFb2NQOVlQMG9jZGRzTmstRDhmbi12ZGFhblRaSnVFT2tGSUg5RGNSZG9tMkhYUnBhOUJvMHJHQWZqNW5hVU9nUm5zMkZtVWpVUzJWWDMyWW94eVFaSG5MNEpxVVhOSEZIekZ1Y19IeXZwX2FCZjBCcTZjZElDcWUxM25FV2xDUXBnV0FGSkZNZ3dzMlpLNl9tdTVqdVlPWEJWS2RDN1dNeHl2Q2ZJOGtJWVprWDFBdXF5Mno0LTFGTUdlUWlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil tem queda brusca; ouça o comentário - Globo Rural</t>
+          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOSGNOWlZSaHBzRUJkY0ZyWnZkOXo4WlRoLWhOYWUxOXNnUkZJZi1YbXlPRktTT1EzZUdydnM3bkFoc243VmtkdllCYVZibnNyb2Q4d0VESVlXamN6OFRyOEQ2XzUyQmg0RGIwbmoyd05tdy1lVUQxV2gwZ3RxT2dpLUlqb3JtVlpmMEdBc0NNYjVsX1ZPZl9DQXVPLTdCSi0ydWRUbVhJZEJleHVOYjhpY29rbWl4amhWdVdGbXF0b3M3Ynd6OFF4SzRxSTbSAdsBQVVfeXFMUE5CZDBKenFqQ3RwamdaNzFjb2ZuSC16ekZSMTFaQVg2S2RFdG1DcTlCai1oRm1halpORjdhc3h1UUE5YzNmT013aGJVTElUX1UzcHdyNTdFc0xQSzR2OTBLNVViR1N4VHB5alpOUC1JdENHS2VOc2ZWLUlYR1hveExIYVdEam5TazZpX3F0bjBtYXlyUFhmcW9lX1hUMW1RNHRxTEJ1YVoyOGFyX0NlNEJ5S3dsanVFY3F2akxfM19oRGhqLXgxc0ppTFRMNzU4aWt2MnJOQkI3N3Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
+          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Preço da ureia despenca e volta aos níveis pré-guerra no Oriente Médio, mas mercado de fertilizantes segue desigual - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4262,19 +4262,19 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgJBVV95cUxOeUFBQ1FzWi1zR05FdmpQQ0YzRFJPOWt0VWZhRnZyQVI5cU0zVUoxR1lSRFFFLS11d1Y3ZDhEX3pscWZVY2Fibk5pbVJfSmxlelVaOGQ2REsyTFlHZFZCR0xUZVFLY3VwYl9BZlBxNDBhck5uUm4tTUxXWlhJcnh5bVpUUzlqM2hZQmhnWlZkUE51YkhISXR6QXRucmU4ME9qN3FDRUpYZWtxdnFTcGVVU0JsaTJ2YkFpbGJGLXJadnhJOXFNbFkzem52eHhLT0ttSlJwcDZJa3NOUVA0aWV5Ml9aWmdNZGZ1MXlMVHZBNDVpR0Vnc2c4ZFVabEduUEFBcnJpRGx6NVNieUZDYXlGSjU0dWFHbm4td2FZNGtQMnNSOUFOdVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4284,29 +4284,29 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Risco de desabastecimento de fertilizantes diminui, mas produtores continuam "ariscos" na hora das compras, diz Mosaic - AgFeed</t>
+          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>22/06/2026 19:10</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxOTDBlYlkzZWxfeVJJZ1RBTmVqclRXV1ZYcDYzV3hxR21VNDV5NkpRRXV3XzdmOVlCNFpXMXFJazJvTWllaFpfVTNObGE5S0JKQklsZUhZMi1GTE9QZG15TklEdUdaUUVmbXdxTmI0emNCdnVmNVFCWkJCN3NnY3FwcmozSzdzUjV2bzhoaElESnlPcVRmbzJXWlpiUkhGSmR2N29IbFE2N2xvMXNRZkV2WTg3aEc2czRWcGN3M2xGLUxtN1pLZTBPa0pjS0xBakVMTGRvMlFQWWg2anB1b1pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4318,29 +4318,29 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>22/06/2026 19:10</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4350,19 +4350,19 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4372,19 +4372,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Visconde supera Monerá e é campeão da Copa do Calcário 2026 - Serra News</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4394,19 +4394,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQdDBrMzFVejA0SWNzMERWbzFwVWNVSm5XZ2lWd1lTQzlqX3BBX09mRFcwZV9Qa2l1WUxNekNKSFZHNFJrekl6TnEzWE9IWW1hb2xVTS1XSzRwOU1rdEtFdzRzWk1SNEdOVTN6VzE1ZTN1Vk9aLWttaFBldUU1Qm1EUFhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Prefeitura de Peixoto garante 1.752 toneladas de calcário para fortalecer a agricultura familiar e aumentar a produtividade no campo - Nortão Agora</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4416,29 +4416,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgJBVV95cUxQTWhuakU3WXV0dkFOZXdxRjRiaDRjOHZUbWVWSjE2ZFFLVEVIcnhkb3BpM3Awd3NBdHBKMDAtRmlxTEt0MGpMUXU5OFNoSlRQQTlGUTJ2Tk5nM1RZb29GaG5abFJEaEJWb1owTHhrTU52REEydVpMVmpabVU0dS1pdllxV2gwRWNORkxwcE9xS1BGS0JWN2t6YzN4WWRWN1dSaTZucHN6M0d5MnBlZlNoVXk5MkVudVctQjljd3lsSUUyTFVkdHZaY2MyT1Z4Q3ZhSzY5bkF2bGREMjkteFJPZFhvY1BWUGhqa0VOT0QtUEp3c3ZGZ2tnM1NRdTVRMmJHTXBtZDlGQlJGOTdiREZ0QTNSUkthdmstOTdiTDBxRHVVNHJoTWZ4eklJZ0U2T2xmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4467,22 +4467,22 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4516,39 +4516,39 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
+          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>19/06/2026 04:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
+          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>19/06/2026 04:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4560,29 +4560,29 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Fertilizantes têm ajuste com cautela no mercado - Agrolink</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPRjZ2d3B2MFRIMEw3SHk2YXBObFNCenQ5cVFDNXNUbTdldnNEaXBQYkRpeUl1X2xXTktsQV9ZMjdhUDF6SEFZRDRwYVdXSG16dl9jRUp4OFRPbVRRZF9OZTJ2UVYyVjMwWFJOZ3BzYV9DMHlUc092ckJGM2dCNkdmUEdFaGJxS1FYY0N4eDI3eE1OMGd5MDZ6WWZZcG4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4592,51 +4592,51 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Freedom Broker eleva recomendação da Mosaic com melhora nos custos de enxofre - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>16/06/2026 14:20</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPYkJCZXRNYmpPWklEMVVnLXVSYlhzYWE3cHc1UXZDcVZWbUlyb1B4bm53QjR4UG5NNm1PMEtTUm1ZUXctb2g1UEx2bXpiSEUyajB4ZHdOb21kZFVPZkhvV1QtS1d3X0ZuWUZ2N3VEV2tQX2UxcnFVbjZBYWNKSVRudGgzRzl6Y3JHWE1lZ3FTbk1rZUtfRGZBTUpZMlV0QzkwdVRKR2Vid3RWcjluY01lUFVFT0p1RGRNRFR0cUwyVzk0dzdyNU9EOFNEZndMeHl5M3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>16/06/2026 14:20</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4665,34 +4665,34 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil despenca em maio: dados de 2018 a 2026 - Farmnews</t>
+          <t>Rio Maior organizou Gala Empresarial do concelho - O Mirante</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPQXpiWmFxZVBJRFo1Q21oUXQ2OXdhMGUtbmtZRTBkcnR0ZnZmSExQOHNBTExlZWNvNG0yWG1XQzhNaG5fNHpKbU1WdTN4WERZa21CYXVUaUp2SkZhZ2xrcjRma2ZDVmU4SGRFVVJNQzlWYkdyUlRIcTY1YW9Fd1hQUTJoYVM0dXgzdHlJNnZ6S3g1ajVCUDdaWjRoRjVBYTc0d2VwZQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYmIwcks0U205THc0UF80M2tqOTBpZWY1VWhZMFZzUUE2UEt2bmFLcTBsQ1g4YjRBRjBmRUZiN25XQVdCNDdldTdiZC10VTdBSzY3YjJiTFo5TXdaNjVVNkZUMTZSQ1g4MU1XX2s0azMwd0hNTFlDTktFVktWSWtrWUpPTjFQZEhoUzU3M3NzaXpQMVVaajZoYWhPRHNtLUhf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4731,12 +4731,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Ureia volta ao preço pré-guerra, mas vendas ainda não reagem - CNN Brasil</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOT2J4STBfU3p3enNZSHhWZjZxcVc2YUp3VDlhanpJMHI4dWVpREtfanF3dWFiV1hiSWN2NWxmMFJqQk1FY0w3Rm43OWVfSlpFS3J5SWM3ZzZnbXJQa25hWVMxYmNCd2QwalBGa2dQenc1NmZVZHJ3U0NxRUxqay1nTHdlMTFGNDR3RUxwRWs4cnAwWF9TVGNlWXc5ZDdiSldlUzFKdzhTRGQ4bTN3ckVpNFV5cHhmX2c?oc=5</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>O ‘apagão’ da ureia - VEJA</t>
+          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,19 +4856,19 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>O ‘apagão’ da ureia - VEJA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4878,19 +4878,19 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFB2TVVHd3l6Y3AzZlNEZHdQYzhDb3BqU1dzX1J2c3JMaElCcTVfcUU4UXFHWC1oWTktSXVHVlZtYzNvcW1ZcnNSbHJ3dG5IYUdQeGw5STVURDY1eGZ5eGxucDZBZWw2ZHlaR2d6Um5MSUt5ZmRJLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4900,19 +4900,19 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes atrasa ritmo, e demanda final ainda é incerta - CNN Brasil</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOM0dQQmMtMGdEM0J3akZiajRvWGVCa3Z0RDZ5dVB4Q0VmSy1vSmx2Zl9IaWdyV2M1Zm9jTUdTNFRXaGlmTmo0SW5ZSWlFcXhXLVNrM1VWdWJsTFNxTGFkZERKQkpUUllxb2xHTy00VVNzSmdUamJaZEhUWmU3SWZURHJCNWx5bUVlSnA2WjF1akVkMFJDWEt2Yjh2MmJyNE1ReGQ3VEp4Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4966,19 +4966,19 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4988,19 +4988,19 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,19 +5010,19 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,19 +5032,19 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Demanda fraca amplia pressão sobre preços da ureia - Revista Cultivar</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORzU4NlNla3ZiNE9CZ3BoTTdKUHhnSVFMR1YzT181Tm9QU0FlS250SXZSckRTV2VRMEIyMGpOOFFFaW9RdjNEZ20xUUs4N2c3WVZxMHlWZE54djd0cDF4c1Z6a3V2ZGstbTBXTXdROXNsWnN0bVV6cFRyTWxhc2x0ZEtrMXE4ckhGSWZSZnRZcGhyRG5r?oc=5</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Demanda fraca amplia pressão sobre preços da ureia - Revista Cultivar</t>
+          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5142,19 +5142,19 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxORzU4NlNla3ZiNE9CZ3BoTTdKUHhnSVFMR1YzT181Tm9QU0FlS250SXZSckRTV2VRMEIyMGpOOFFFaW9RdjNEZ20xUUs4N2c3WVZxMHlWZE54djd0cDF4c1Z6a3V2ZGstbTBXTXdROXNsWnN0bVV6cFRyTWxhc2x0ZEtrMXE4ckhGSWZSZnRZcGhyRG5r?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,19 +5164,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,19 +5186,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,19 +5230,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,19 +5252,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -5274,19 +5274,19 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Preços da ureia acumulam 25% de queda; o que isso significa para a próxima safra? - Canal Rural</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,19 +5296,19 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOZ1daY2E3S1J5SkVNUnpBSjd2N0kyWTBpY3o2MTNBRno4UFNoeVhQMzJiUFhVb3dZXzFmRnlES2dqcHpfRFQyS3Y2UTBUdXk2UUpNY1FubFA1eFMzcnlSblFvRVljSUNmYUN4SWdFeURZSm42YkEwWnBic1hYMy1VRDIydmNEWTlIWnI2SHJXMHlvdGRYcUdqSjFNdFU5LUd3V1A0a0lfT1pnUXlpMU5kZ0IyNXhFRi13ZnI3a2F3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,19 +5472,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,19 +5538,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,19 +5560,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Empresas já investiram 42 mil euros em bolsas para estudantes de Engenharia de Minas e Recursos Energéticos do Técnico - Record</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmFyZTFtaDlxMU53dnBYVHctWjlaYjgxWENtckgwTGc4c3RGTXJONGJzV1ZfcVR0UkxDX25pMjRGQzVPaGd4VmhsVGt1LTU0c1h6NVpVRTdNRFRwTU9aVi1HVDh6Sl9fN2dqT1FHeVAwNzVlM2pSTE5ySFk1akxwT29HcjNxM09QcHFMeDlGWUxXQ3RIV2dsSGlKT1UzLXpBVGVTaTd2SFRuMGVLZ3JwVS13cEJyekN0RGRacVBWY21HeXNZSXlkVjRBdDQwSmRqVWFBdGVnTTVDY0xHRnRkejVJeTVQcEFEQ0dfRWlEZWxXWFQzX3VtUnlDWWVMZVlKRWfSAfwBQVVfeXFMUHk4ZkRPbFJnd21WaVVLQURqWk1WOVByTVotSmhwNHZfRThVWThRQ2Y3eWE3RHpVU2gzR0p5c1dIMzFDdkdjNXBPejF3ZWo5bnM1QWtWWEhWeXNndGNCY3VXM2UtYVFXZ1cxZlAyZ0pGd0N0ckZRNmhINW1yQS1NMzZMUzlfa1FDMksyckV2MHRXY05tcVUyLXpvNXpVbnROWjcyTTFGNHViOVVDNlVGbkk0eTZtNVprZ1Q5Tl90NWdNUTJFZGlBUzZQMDBnYzlsUEprWGRYcVZQM3hJa2U4cUhVbHA3MklRSjNCVkFMSXIwSmF3eDhrZjliTmlp?oc=5</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher coco ralado por excesso de enxofre; veja se você tem em casa - Exame</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5604,19 +5604,19 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNZzd6c1RaVDEtMFk3TnFhekVMSDNOQnAyUkVxaHkyQklSbWMwYTQ4b0tFSVJtTGZ4R0pONmthWmFOWDRNRTQ4YnFjWkh2ZDFfdlA1VGFidmpTQTVQdUxMaWpmd2Y5QldZZkxlQ1U5SHdHa1hOMzVUQmV3bzRJeV9GUDE1b0FMRE5sOVByV3pJOHNOWTBxNGhWRkRRbFM3SEppcHNCR3RrNHQ3MUU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,19 +5626,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Empresas já investiram 42 mil euros em bolsas para estudantes de Engenharia de Minas e Recursos Energéticos do Técnico - Record</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,19 +5648,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxQZmFyZTFtaDlxMU53dnBYVHctWjlaYjgxWENtckgwTGc4c3RGTXJONGJzV1ZfcVR0UkxDX25pMjRGQzVPaGd4VmhsVGt1LTU0c1h6NVpVRTdNRFRwTU9aVi1HVDh6Sl9fN2dqT1FHeVAwNzVlM2pSTE5ySFk1akxwT29HcjNxM09QcHFMeDlGWUxXQ3RIV2dsSGlKT1UzLXpBVGVTaTd2SFRuMGVLZ3JwVS13cEJyekN0RGRacVBWY21HeXNZSXlkVjRBdDQwSmRqVWFBdGVnTTVDY0xHRnRkejVJeTVQcEFEQ0dfRWlEZWxXWFQzX3VtUnlDWWVMZVlKRWfSAfwBQVVfeXFMUHk4ZkRPbFJnd21WaVVLQURqWk1WOVByTVotSmhwNHZfRThVWThRQ2Y3eWE3RHpVU2gzR0p5c1dIMzFDdkdjNXBPejF3ZWo5bnM1QWtWWEhWeXNndGNCY3VXM2UtYVFXZ1cxZlAyZ0pGd0N0ckZRNmhINW1yQS1NMzZMUzlfa1FDMksyckV2MHRXY05tcVUyLXpvNXpVbnROWjcyTTFGNHViOVVDNlVGbkk0eTZtNVprZ1Q5Tl90NWdNUTJFZGlBUzZQMDBnYzlsUEprWGRYcVZQM3hJa2U4cUhVbHA3MklRSjNCVkFMSXIwSmF3eDhrZjliTmlp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>China libera cotas de exportação de ureia e alivia pressão global - CNN Brasil</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPeWZUcGlPVTM1aW9Nak5sZXVITDhRV3FndUlKQUJqMElZUUhWbmoxdDk0Q2ZNVUVmbmlSdm5pZ1lxWHVYT3ZqMDdPSVZSSTBiWlJEN1drblFHc0dCOVFlMnBmclpTWGFZN3hxbVZwQk9TdkktQmVzN1VFWHhEQllTSi05UUpXSjZydVJOcFQ4VmxaSnM2eG1pQ2QzaFR6RkJNTlE?oc=5</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>União Europeia suspende por 1 ano tarifas sobre ureia e amônia - Canal Rural</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,19 +5824,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRlFPMU1SeE1Vc2xQZWRPQ0ZzMWtzZ00tTDBvWDNXdjNTSllpMG9FN0ZjS0ZQNVhRby1xVDJRWC1SVE1abmt4ZE1QV0xvbHgwOEZid3ZzYlMyUHlXUFNVa2pFRzI2WDJLRzdxOWdrQnVlMloxNC1oQ1VaaFpVV3hsQ183a2d6ZkI1Wnd6dUFrbmtsY3FQVmJ4enNJbVdWQTRNeDFRUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>União Europeia suspende por 1 ano tarifas sobre ureia e amônia - Canal Rural</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,19 +5890,19 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRlFPMU1SeE1Vc2xQZWRPQ0ZzMWtzZ00tTDBvWDNXdjNTSllpMG9FN0ZjS0ZQNVhRby1xVDJRWC1SVE1abmt4ZE1QV0xvbHgwOEZid3ZzYlMyUHlXUFNVa2pFRzI2WDJLRzdxOWdrQnVlMloxNC1oQ1VaaFpVV3hsQ183a2d6ZkI1Wnd6dUFrbmtsY3FQVmJ4enNJbVdWQTRNeDFRUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5912,19 +5912,19 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6066,19 +6066,19 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6088,19 +6088,19 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6110,19 +6110,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6205,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Mosaic e Inpasa assinam novo acordo de barter focado em insumos - CNN Brasil</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6220,19 +6220,19 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVm00RUZmWGVBMzJ5Vnc4aDB3ZktTenoyMmJXanVXWF9xYTlNT3VmalhFbk9lYlNiT3h5cFZMdk5qZ0xkUkpTMkM0bkxhNHZvRk51SDZENWliR3FmRUNxMEFJQ3d5U3FNb2hhRUdCWUs2X1UxeFgzQjhMbmItbmhaSzhyQkVFSHF2ZV81UWRVb2VDTF91cnVvVGNZSW0xU28?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Queda da ureia ainda não anima compradores - Agrolink</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6286,19 +6286,19 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVk56WkJGR2cyN2hvcW1MLVNPS3BudEVxRlVUeEFFZVgyOXFlZ1dKUnZoOUo0VmxOaVc3bFM3emFTTkhDZDhPRkJsNDFUcXFYODh0ZmlPNFRTb1dKLVNEalU5cFpVMXJFdHJKMXFUUkZMOVA5U0d4Q0pkdW5JSy1zVVprSHRKX1BITkRWVmVoaXc4dm51d3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,19 +6308,19 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Queda da ureia ainda não anima compradores - Agrolink</t>
+          <t>aumento dos preços do enxofre em meio a crise global de suprimentos - Sunsirs</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPVk56WkJGR2cyN2hvcW1MLVNPS3BudEVxRlVUeEFFZVgyOXFlZ1dKUnZoOUo0VmxOaVc3bFM3emFTTkhDZDhPRkJsNDFUcXFYODh0ZmlPNFRTb1dKLVNEalU5cFpVMXJFdHJKMXFUUkZMOVA5U0d4Q0pkdW5JSy1zVVprSHRKX1BITkRWVmVoaXc4dm51d3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1rQ09LNEtPX1l6VWFRT1VRTG9ZWmFtM3pRUGExdXJXVlY5V2RsLURoNk5vT3N2b0p5MDZzQkZsLWtkM3dtTDZSd1VQeVJra0UxZ1QtRzJIdi1ndFBwdWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Macuco, Monerá e Altense estão na semifinal da Copa Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQelB6RDJLanhUTVA5cXJpcC1aMlhDRmJuWnJ3SVl4NGFCWTZPbVI5VW9HcU0xMXd6bEZIQ0tWYTNQejVJQkl6Nmcxc0Z5aS04VEhoNy1qLWNoODdwTmg1LWpMWHRCWVppUkdTLWNQNGlZSU5XQ19BVzFualhvYnFBUXNLejdJWllLQTZleEFLMVI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6660,19 +6660,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Margens derretem no Brasil e Mosaic começa 2026 no vermelho (mesmo com alta na receita) - AgFeed</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxORklOTkFqdEJTSkRkVUgwalFVWjdVOVNRTjZzOFBhS1h4Xzl1YnM4dU56QWY3UnFHeVdpaGNFdnVwTzctWURPQUVwZExqN1MzZWYwemxndGxVVE93eUxybzEzQVFxbkVWWVJhMU5hOHU5TGpUTGNRZ1dWVXRuV2xBNHZBMUprWEpYYnYyX3Y3ekhRbVNvWWpfSVpYZ1NTeURnOXJfc1Z2eUFERkh5TlZGUjBmMzlKS1ox?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6711,12 +6711,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,19 +6880,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdHVNT3dGcTBxcUhOdFp4a0NoWW1lZDBQa0xiWEZpYkFoYTZxT09fQTJvNDIzdnpYU1RNbGtrdFVtUUp0bnJrcWRMeXlsX1lJRE5vUXY3RlJJM2VvVGRWTm5aWUhpTzJ0MHZiUW10em1EZzI4bHVmck1CVXdhSEdxVDFfRUIzZkdzN2Qyb1RWWWtiNjZDRlpKYjNra04?oc=5</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia na Ansa e reforça estratégia no setor de fertilizantes - Exame</t>
+          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNN2FLdVNOLVNmQ0NMUEhuTkF6bjEyQ3FnQXdxM2FoX21YcEtGdG5aZUh2MzNPa211NmlxY3BnMWVDMHFuUXVER3g4U3l6Q1VkS2pGbDAtMkZJenBlLXJFTnp4U2dqT3pyRTZkcUp0WFRZT2piVFVYNnJJZTNCd2VKSTBLeEJPbzhvS3UxdEV5eW96RVhiY2Z3OGdpZ2F3THV0dVR0MW9PRE5XRUl1bEhsYTlWN041NG1hY1VYdHVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ureia inicia movimento de queda global após dois meses de alta - Canal Rural</t>
+          <t>Petrobras retoma produção de ureia na Ansa e reforça estratégia no setor de fertilizantes - Exame</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxONUk3RS1YMGFVeTl3VFlxaTNTcXQxMmtGNHYwdWh4MzlWZmlHaFZUNDlhX3hFY2lEcXdnR0ZaQVFRaE5VN2JOUE82LXI0blB4V3cwRmZ6aUN3ZVhacnFmZVhybEVtWWlrMHV2TG1KUGZhQVRqdDNCeXRKeUd6bWxlMGNsWjdnV0JOQWQtSnFvaDdlU01zSVRkcE5RbWx2bjU2OXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNN2FLdVNOLVNmQ0NMUEhuTkF6bjEyQ3FnQXdxM2FoX21YcEtGdG5aZUh2MzNPa211NmlxY3BnMWVDMHFuUXVER3g4U3l6Q1VkS2pGbDAtMkZJenBlLXJFTnp4U2dqT3pyRTZkcUp0WFRZT2piVFVYNnJJZTNCd2VKSTBLeEJPbzhvS3UxdEV5eW96RVhiY2Z3OGdpZ2F3THV0dVR0MW9PRE5XRUl1bEhsYTlWN041NG1hY1VYdHVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
+          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6968,19 +6968,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Preços da ureia cedem após dois meses em alta - Globo Rural</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPQTFfM1dYaG9xa0s1eXk4bXRQb0d6V2Q0NzFvOEJ4dlB2b2NRMlkxRE5ZZUZQdlV1ZFdyWGljN3Z5RVRFUTVuTjZ4cDIyUDdrZWpWMUJtNHJrZmxsWV9zZkRobXoyd0VBRXFvYXB0WDFsSC1vMDZBN2haLXYyUFp6UWtzQTlYb0xSMERMWElPN3FZSDFQN0l4ckd1U3RIaDM4cnRNNUoyUdIBtgFBVV95cUxOVlRkd0NYWjUzZEhHblM0eGlJdjlNblRaWDAwWWlNclRFbXVYY3VBQmczNVpEdWdzOXJqNHY5dUVZVWVYMzNsNHNsRTYxenZkMXRqQkNYUlU3YWxWajc5NmZld2dwRmRzaER1T1lTdG1KZ0hUdVJqeW9kNDBjWTRfaHo5eG1oZThZTzVsQ0M2aXljcURYWk1YWGdxeno1M1JkTTlZZjVKR2x5U2xrTUNSeUJfMmRJdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Após forte alta, preço da ureia começa a cair, mostra levantamento - Canal Rural</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcUZLcjlzMlFBNFM4Nlo2U2ZYdk1hc2YyOGg3Rng2VThuZVY3cXk2V1BXNWFjaWQyb3lvbnM1d2E0b1BwVFYwZzhEX2drSWxyQllLQlM5S25Uamd6U0pYTVo0cjFjcjRHMGJVXzQ0SUM3V2tIR3hpTER6NjF0OUZ2T1VNNWxyeWloRjlTRDlqSkhtcTFBQk50akZscERXME9DRjF4dWtnaGRvbFU?oc=5</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7078,19 +7078,19 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObWdVQ1R0NC1YZThsV1NPR1p3bnY1S3JpZ29Rd1l5dWtYNkUycTlma1FrUUNmLU91aF94eFlSa01qMmszRUgzWkoyd0xQWnhHS0RDRF9oSnd2N29lQUROVDhiUzJjUmlWcWw5SDViQnh3MWY2SGJiVVREX1dyYkN3S3RsWnlfcTBX?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,17 +7112,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Fechada em 2020, fábrica de ureia volta funcionar para reduzir custos do agro - Cana Online</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZnQ1akhGT0dxMDFrQ0ZJTVI1UllvbG40eUJmMTczWGFHOXFVYXlwZUhiWmxoR2VDZXp2b1hVaVlEbkpjNkxFbnJuY2swZTQwb2JEdW01Yk5KY3RFdXRPTnNlaC1xeGZmdEFFNDFJamMyQkVhZXUyOXViOXE4NDlZX2VmSzVTZTRzdTZ4Vm8xaEppa3lNTjhSejlUR3dtakVhNnNmTUI1SWltRmZhZC1YS05FeHhLc256Z0hn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7134,17 +7134,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
+          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
+          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Em meio à crise dos fertilizantes, Petrobras volta a produzir ureia no Paraná após seis anos - VEJA</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNU2E5eUdWYzFxMHoxdzFrdktxNndmLXhpOC1mY0kwcUVPdWpoVnVkZVgxRXZQY1N2UFJNRmozQ0p5UVlWREZKaGFLMWR6WUU0UmxSTG5xaE1lSWJ1QjdaOWhMQVNUY29Lams4WnE3bS1Tb3JhaUR6MDJSbWtkUU9ZOGlvSS1IOHFWSGJjY01PYTBkN1d0UE5xWHZTTDFmUEpiUTEwN1BQWWNpZnRXRjBxLXR4MktvUWJOMzRfVVl5TWNwRENEUnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Petrobras retoma produção de ureia após 6 anos e avança no mercado de fertilizantes, na B3 - ADVFN</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQaWlBMEcxWUtKWXVyOXU3dU95dGV3MUpDd2RkanlxMXZHUE91UTJVRmtzbXRfUm4yMnE5Zm5udUo2dm1vSEdYRVNMckxQcjVQamlvUDctYkNsQlJXSmNXaHc1SDBmOXlzLVJhaXRQSmR3Rmoya3hmcERRNTUyTmxFZ1lQNS16UFkxUEpMMEh3U2YwdEFYUTRUMmp2WnVTMVhMRWJ3MkhzN1A4cTVKeHhzZURmN0FIWTkzRnN2ZHJZcjd0MzQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em usina desativada há 6 anos - Poder360</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -7320,51 +7320,51 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPRGJmX0JoNWk0dFFBRGRrcXBleVZaUjVud1dPakQwcUt0X25QUTFEUVh4N0MzWDVTRUlJZ3NOaXF4cWNfZkktckFlRGRTRlRYRkNKOXJFSFI2VlRKUDRMOVpUWWM4b2NSa1NYM2VtX3FSdUVwZ1U1LVJDcVJTc0FoMjN3Ui1RWkg5MF92Q0FXLTRocDZMUWpfR1VIbVVmS01qWGYxblhFTm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7393,34 +7393,34 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>CMOC assegura projeto Cangrejos por US$1,7bi no Equador - BNamericas</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUDFMYWdTWDQ3ZGljdUF2VDY3UkRwLS1xNXBxLWZQVEpEMG5nU1dvTjdqZ0lyZ2JFRC0xelhXR2FINldleXlJWUJDOTBwU0NEQm14LWlqNVFOcWVPc1Q4a0tXWTNQYTFkZThzUkE4MElVeXBXOVdqaXZUNTJyQlpIMFhzX0xXclg4QWtqR1kxOVZES1NyVWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -7430,19 +7430,19 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -7518,19 +7518,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -7540,19 +7540,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Justiça anula licença para extração de calcário em área quilombola no MA e determina indenização de R$ 100 mil - G1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxQSi1hWVV3Y3VUZmNsUEFqcTVlc0lpUzZEMnBYWkdGNnJRVXU0WFF6LXkwRlVHMEFCMnRPbTVzbHJSS3BXTGI3WnpMOUVKSlJ5ZjBHSGZ1WXF0NkptY05fb0VvVzdDa3BlLXFYamQ3YTBFWWpGUi03cXZzbWJkZlFjQVRGS0lEUl9haDF1U0lfbDEyQ0ZkZ19EcGhCMzZ5d2ItYURqX1NMMUduZ2RzeGt2UUwzZ0NteVdPaUwzM0ZadnV0TnhJS2lrbk1JMnVaRkkzQlBUR2FjNWFpRnJwX3JpVWhrSUk2bjF2d3NBcVVSdVJzWGtpZ19OSW5jUTZ1Z9IBjAJBVV95cUxQdU9IMnNVTTlweXVDZ1lrR2VZeVlNdC1vQk00YVBGV1U1ajdjM0lDZDdTcmVxNF9SX2N5dWdfSVZwVFktSVVrTnZUNE9pWFQyNkxGM1VPMHg3d1l6R0Q4alZwMENMUkdTcUlydjRjYzFSZHJqTDJnSll0MHZlUVhxbnY3YmJjcXVmc1VYaE95TFRmZlBVMl9ZaTZ6YzN6UnRvUVdLekZNNC10QjV1Skwxd0tKaWxfeUphVE1QOHBMZUVzMk5MWjhfVGJLNG43TzZobmtRUFhERlpXVjlsZzZiY1l6dWU1ZGhhQjJhZVhta1FkTndJMkpwYUpVb21OVEN1S0RlLURxWUVjd0ps?oc=5</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7694,19 +7694,19 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Alta histórica do enxofre eleva custos e pressiona cadeia de fertilizantes em 2026 - RADAR DIGITAL BRASÍLIA</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaFZWeGVvRU9TMG5XZlBvZ3JiRGU0UlpKS1lucmlueW9ncG0wZnVFOFVjRWFJRVRiVm1Ua3A4UVhQdU9hcXdGQWljSmhmcjRyeTlZY2FVR2xWOENBZzd6THRnZVJVMGlmd1R0Y3o1aFM5WWlWMXpieHpBQ1FucDkwLS1MZ0VRRnJ4aG5YWk85dDNjNkplb0xkbTU2cFVzMDc3bFRydktaMFI3X3FWRHpMS3g3Y1VrMmJSR2Nwdk1MU3plaUxGU3dUd0p2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7826,19 +7826,19 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7848,19 +7848,19 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews - InvestNews</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -8134,19 +8134,19 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
@@ -8266,19 +8266,19 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec3bab247adac737658ff8cd917&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbad11b472396ea0e332a9f7670&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8383,12 +8383,12 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -8398,19 +8398,19 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -8420,19 +8420,19 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - UOL Economia</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -8442,19 +8442,19 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNa3NxR3M5LVNsS0lzRzRHWGRWbDd3bThGS2JLbkdvY0I0MW9ZUDl2dnk0YTJlbk13Ri1meWxYY0NtbjRtRW13aVo3eXFCbWdRQXk4bzNLYUxEZUJkMXlJODZtcXhYdWVGZE04WTF2TDhMTVh0RnU0SGFzamRkLUhTdXVKR0RxZWVRRU5KLXF3WEVOd18xWGdzNTNuS0NJOWhhc0FoYkZiX2FwRUY4d1A4UmV1c2V3d3RVZGhwUC1WUlF1ZnNXRDZmUl9Eakdvd2NuVUdodlVUVEZhZ0xKVDh4d0NQcVE2X0FqdHZPUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -8486,19 +8486,19 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -8508,19 +8508,19 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -8530,19 +8530,19 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8816,19 +8816,19 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Prefeitura de Santa Cruz abre inscrições para distribuição gratuita de calcário a produtores rurais - Portal Arauto</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8838,19 +8838,19 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPZjd1TFdpbmV2Ui03ajM5WE9GaWNPUFZ3bVJJd3h3Q2JOdU05Q3Q2c0V1Y1FObVJFXzRTbWg3RVZXVzd5YUd6bXltMGEteUZ0WG5aUzZVckhwVVBBX3ppbDZ3S1NCZ1pnM1hHQlZwcDAxQ1pfa0FjNlFHOHRocHlvdzdvaTlON2lVdjJtaHRfRnpiRkFhcElYYmMtc1ZQTVlTQ3hFMnRLNTRlU0w1VjE2UW9ZUXpzcy02SHRDUGNLZDRhSDRqV3kyRUlPVWRKRjQwaFpnVHZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8860,19 +8860,19 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8882,19 +8882,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9021,12 +9021,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -9036,19 +9036,19 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9351,22 +9351,22 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Preços domésticos de enxofre enfraqueceram, enquanto os preços do enxofre portuário permaneceram firmes - Sunsirs</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpUHpyeDNlaGFXZGtXb0JTeV9CaWVmTEpQZ19FWmVIaC1kV0J6amJVUzRZRVFOU1ZIVWhaSEtQSFE5ODZ0SEROYnV2OXVINXJnQXpUZ3JTV0g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
@@ -9378,39 +9378,39 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -9439,34 +9439,34 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -9476,85 +9476,85 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>02/02/2026 05:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>CBIOs iniciam 2026 nos menores níveis históricos — o que explica isso? - JornalCana</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>02/02/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPUy0wRmhXSWpaNGxjeGI4TnFobWctR2ZFU1ZpeHlhRlRqVG5KQXg5dXd6MEhKUWU3NkFxTEtHX2RLTFk3blFCbkFDZ3V3YXpCMFZkWDhDTlFTdDBsc21HZTFtUXBLMXdlRHFUR2pyT2xUenZUTU5Xa2dmMzRBc25qY3pnZ2UwVlBwQ3RUTm5rSTAyUlRGcHNFTF91N21WTnI3bGdFcjRZdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9598,17 +9598,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9637,22 +9637,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>25/01/2026 05:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
+          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>As ações da Mosaic caem após vendas fracas no quarto trimestre, com a demanda por fertilizantes em declínio - ADVFN</t>
+          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPczNSak5ObDg2c3FjS3J4eHJ6aW5ZN2k0SF9UYUVtQ01fdmFPaDhscjROUDA4QWZKVFhiR1ZWaTBab0t0dVlaT3FoeUhIVXhEUzIyT3dSdGpXMjJUS05UYVF6ZWZKZzZPVkptY1FzdVN2Rm9GbUpHblNVRHlLbS1aUlJzaVBrZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10016,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -10026,19 +10026,19 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -10092,19 +10092,19 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -10136,19 +10136,19 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,19 +10158,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10209,12 +10209,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -10224,19 +10224,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>China CMOC compra quatro minas de ouro no Brasil por 863 milhões de euros - RTP</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQV0FjeGVtTGVqd2VhNU5fanJxQVlOSWI5ckFnZTFhLVgtdjZQNXlzUUFIYVJhS285THFzZjRiNUw4QnJJcENRVmtQT3l0NUVzR3c0UzlnT3I0anItNXprX0Qzd1R2b000V3Bya3NsSVVtMi16U2JQaERkcFZQRVFxalA1cTByWEVjTzZKQjc5RHZrdWdncy1zWEh6ZURSTFJXWG1HdlE1cV9iLXpMRG1sVWl4R0ltNDF5VHVJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Agência de Comunicação - Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTDRHMUtOeFVXOTk1NlEzYnRSVU04ZUltZW5TVWQybFZQdmFwdGV0YkdqMVk0VXQ5YXJHQmpXelZyUDlUcTZLNFA1NnlXS3NLX1pSYXlUaV8xbkdxSktMcHlma3VWMXRFSWZMbGRobU1NX1pyeGRSd0d6VXZvS0N6azZ0NklzWnloN0w2ZnFod045RFRfWloxa3Z4QlhFTE5YQTR4WnpnRUNBUTBtZWFRRW5IRk9MVDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec433e346aba2877a1ee7ce9b8f&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbb51504aa7a43c7f394426b4b3&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -10715,12 +10715,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -10730,19 +10730,19 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec3bab247adac737658ff8cd917&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbad11b472396ea0e332a9f7670&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec433e346aba2877a1ee7ce9b8f&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbb51504aa7a43c7f394426b4b3&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -10979,12 +10979,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
+          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10994,19 +10994,19 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>O Caminho do Peabiru é tema de seminário na Unila em Foz do Iguaçu - Brasil de Fato</t>
+          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQSXdlQlZodk0zOGYzclFlMzhEZEJIOUhhRy1YMG9MVEdCUHR4VUhlNFQ4MG1MQWppb2xBQ3VYMFg1ZnVjSzZMbnA1WXJISldSYkFfLTF4RVpvNHBXUnFIaGpzNVFYalZQbEZiSE9oTVpnTUJyb0FOTHdkTGF3eWg4ZWRCZ3JjQ3ZSRE5EYzNjdnktRXBMbnViMHlTaDBHaDVOU0RobzQtNXZMakNpeUUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
         </is>
       </c>
     </row>
@@ -11067,220 +11067,220 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Calcário: o insumo que transformou o Cerrado em uma das maiores potências agrícolas do país</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>09/10/2025 23:34</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec02fac4d1d93d8fb6d4b007d64&amp;url=https%3a%2f%2fopopular.com.br%2finfomercial%2fcalcario-o-insumo-que-transformou-o-cerrado-em-uma-das-maiores-potencias-agricolas-do-pais-1.3322503&amp;c=8695352406975221608&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>02/10/2025 04:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>02/10/2025 04:00</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>20/09/2025 04:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>20/09/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>08/09/2025 05:38</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbad11b472396ea0e332a9f7670&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>08/09/2025 05:38</t>
+          <t>05/09/2025 04:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec3bab247adac737658ff8cd917&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>05/09/2025 04:00</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbad11b472396ea0e332a9f7670&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec3bab247adac737658ff8cd917&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -11309,22 +11309,22 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>22/08/2025 04:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -11336,257 +11336,235 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
+          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>22/08/2025 04:00</t>
+          <t>19/08/2025 04:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
+          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>19/08/2025 04:00</t>
+          <t>18/08/2025 14:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5cdcbb51504aa7a43c7f394426b4b3&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>18/08/2025 14:00</t>
+          <t>15/08/2025 04:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a5caec433e346aba2877a1ee7ce9b8f&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>15/08/2025 04:00</t>
+          <t>13/08/2025 04:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>13/08/2025 04:00</t>
+          <t>11/08/2025 04:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
+          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>11/08/2025 04:00</t>
+          <t>06/08/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
+          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>06/08/2025 04:00</t>
+          <t>02/08/2025 04:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
+          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>02/08/2025 04:00</t>
+          <t>01/08/2025 21:12</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>01/08/2025 21:12</t>
+          <t>01/08/2025 04:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - IBRAM - Mineração do Brasil</t>
+          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>01/08/2025 04:00</t>
+          <t>31/07/2025 04:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNUS1oVVdaYlNDQXh3VnlEd3Fsclg5UTI5VGxKQ0ZoVzNhRF9obkZPeWg2V3RZN1N3SmhGY0FYZ0dtZVV1MURfQmdEYVJ3cWpUVlNQY0lHdkp0bkQ1RTZXbFZnbkpha292TnZ5V3pxLW1LMjZDcVNiRk93Vm1KRmRRQlJSeEVRZEJJQWtzSElKX3ozaFJTMjdnOUNjUnF3S0duODYteQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>31/07/2025 04:00</t>
+          <t>29/07/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>CMOC</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>29/07/2025 04:00</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
         </is>
